--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,6 +462,1804 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 21/3 , SHORT - 71 - 27/0 , ALT -  - 18/7</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (15g/-5/%40)
+I - TP5/20G - %75 / 32 işlem - ADAY (7g/-5/%77)
+Q - TP5/20G - %73 / 30 işlem - ADAY (3g/-6/%64)
+X - TP5/20G - %90 / 21 işlem - ADAY (15g/-5/%0)
+Y - TP5/20G - %70 / 23 işlem - ADAY (15g/-5/%38)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>339.95999146</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 24 - 12/4 , SHORT - 7 - 3/7 , LONG - 10 - 9/1</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>X-TP2/10G, H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %85 / 48 işlem - ONAY (9g/-3/%38)
+H - TP2/10G - %77 / 73 işlem - ADAY (6g/-2/%44)
+H - TP5/20G - %60 / 20 işlem - ADAY (6g/-2/%67)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 26 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>94.78289795000001</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 38 - 16/1 , SHORT - 21 - 8/8 , SHORT - 45 - 23/9</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (2g/-1/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (2g/-1/%85)
+H - TP5/20G - %60 / 20 işlem - ADAY (2g/-1/%70)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>376.96499634</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (7g/-4/%35)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>305.64001465</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 54 - 21/1 , ALT -  - 13/3 , LONG - 1633 - 20/11</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>309.48001099</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 33 - 5/5 , LONG - 33 - 5/5 , LONG - 33 - 5/5</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %81 / 26 işlem - ADAY (4g/-2/%50)
+T - TP5/20G - %86 / 28 işlem - ADAY (4g/-2/%63)
+Z - TP5/20G - %65 / 51 işlem - ADAY (7g/-2/%65)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>135.11500549</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+ALT -  - 16/5 , ALT -  - 14/3 , LONG - 3 - 10/0</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>I - TP5/20G - %75 / 32 işlem - ADAY (12g/-6/%63)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>36.24509811</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 33 - 9/1 , SHORT - 33 - 9/1 , SHORT - 33 - 8/2</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (7g/-6/%35)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>13.56999969</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+SHORT - 7 - 2/16 , SHORT - 7 - 3/16 , SHORT - 11 - 5/5</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/0/%35)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>572.79998779</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+UST -  - 0/22 , SHORT - 7 - 3/19 , SHORT - 7 - 5/18</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (12g/-1/%70)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>500.25500488</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 6 - 0/18 , SHORT - 7 - 1/17 , LONG - 1135 - 8/8</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (16g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>374.77999878</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+UST -  - 2/12 , UST -  - 2/12 , SHORT - 15 - 6/4</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-1/%35)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>88.18000031</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, NDX 0, TOPLAM -1, ALMA
+ALT -  - 14/3 , LONG - 33 - 8/3 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (7g/-2/%75)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>781.0599975600001</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 11 - 9/3 , LONG - 33 - 7/5 , SHORT - 7 - 5/5</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %85 / 48 işlem - ONAY (7g/-4/%50)
+H - TP2/10G - %77 / 73 işlem - ADAY (4g/-2/%70)
+S - TP5/20G - %63 / 48 işlem - ADAY (10g/-2/%50)
+Y - TP2/10G - %77 / 31 işlem - ADAY (7g/-4/%63)
+Y - TP5/20G - %70 / 23 işlem - ADAY (7g/-4/%75)
+Z - TP2/10G - %82 / 60 işlem - ADAY (7g/-4/%58)
+Z - TP5/20G - %65 / 51 işlem - ADAY (7g/-4/%65)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>361.1499939</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+UST -  - 3/23 , UST -  - 2/23 , UST -  - 4/13</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %81 / 26 işlem - ADAY (8g/+2/%100)
+T - TP5/20G - %86 / 28 işlem - ADAY (8g/+2/%100)
+U - TP5/20G - %60 / 155 işlem - ADAY (9g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 69 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>140.38000488</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 6 - 11/2 , SHORT - 6 - 11/2 , SHORT - 4 - 9/1</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (3g/-5/%65)
+S - TP5/20G - %63 / 48 işlem - ADAY (6g/-9/%71)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>924.03497314</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 22 - 9/2 , SHORT - 4 - 4/6 , LONG - 410 - 16/9</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/10G, Q-TP5/20G, Y-TP2/10G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)
+Q - TP5/10G - %60 / 25 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (0g/0/%100)
+Y - TP2/10G - %77 / 31 işlem - ADAY (1g/0/%100)
+Y - TP5/20G - %70 / 23 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 24 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>211.94999695</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 45 - 4/8 , SHORT - 28 - 3/7 , SHORT - 62 - 4/6</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (5g/+1/%100)
+U - TP5/20G - %60 / 155 işlem - ADAY (8g/0/%80)
+Z - TP5/20G - %65 / 51 işlem - ADAY (8g/0/%63)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>88.86000061</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 4 - 4/8 , SHORT - 4 - 4/8 , SHORT - 2 - 2/9</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (5g/-1/%70)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>503.07998657</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 33 - 17/14 , LONG - 33 - 13/11 , SHORT - 4 - 3/7</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-3/%53)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>35.65999985</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 10 - 8/15 , SHORT - 10 - 11/18 , SHORT - 4 - 5/7</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/20G - %63 / 48 işlem - ADAY (10g/-10/%50)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>54.22999954</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+SHORT - 4 - 1/8 , SHORT - 4 - 1/8 , SHORT - 4 - 1/8</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (7g/-5/%50)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>264.54998779</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 8 - 6/10 , LONG - 36 - 15/15 , SHORT - 7 - 5/5</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/-3/%30)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>78.02500153</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL +1, NDX 0, TOPLAM 0, ALMA
+SHORT - 7 - 5/14 , SHORT - 7 - 5/14 , SHORT - 1 - 0/9</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/-3/%35)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>27.53000069</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+UST -  - 1/16 , LONG - 50 - 1/17 , SHORT - 153 - 8/12</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (15g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>51.49499893</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+UST -  - 4/13 , SHORT - 16 - 0/14 , UST -  - 2/11</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>168.69000244</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O27"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2120,7 +3920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,6 +462,1739 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+ALT -  - 20/2 , LONG - 1 - 26/1 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (16g/-5/%40)
+I - TP5/20G - %75 / 32 işlem - ADAY (8g/-4/%73)
+Q - TP5/20G - %73 / 30 işlem - ADAY (4g/-5/%64)
+X - TP5/20G - %90 / 21 işlem - ADAY (16g/-5/%0)
+Y - TP5/20G - %70 / 23 işlem - ADAY (16g/-5/%38)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>341.67498779</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, NDX +1, TOPLAM 4, İZLE
+ALT -  - 14/1 , ALT -  - 14/1 , ALT -  - 14/1</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (8g/-3/%30)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>307.7250061</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 39 - 15/2 , SHORT - 39 - 19/12 , SHORT - 46 - 22/10</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (3g/0/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (3g/0/%85)
+H - TP5/20G - %60 / 20 işlem - ADAY (3g/0/%63)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>378.82998657</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 34 - 5/5 , LONG - 34 - 5/5 , LONG - 34 - 5/5</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %81 / 26 işlem - ADAY (5g/-2/%38)
+T - TP5/20G - %86 / 28 işlem - ADAY (5g/-2/%50)
+Z - TP5/20G - %65 / 51 işlem - ADAY (8g/-2/%63)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>135.02999878</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 20 - 12/17 , SHORT - 43 - 16/5 , SHORT - 3 - 7/5</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>58.36000061</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 35 - 14/3 , SHORT - 8 - 5/5 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (7g/-4/%37)
+H - TP5/20G - %60 / 20 işlem - ADAY (7g/-4/%63)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>93.29000092</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+LONG - 1 - 18/3 , LONG - 1 - 10/1 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>317.36999512</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+ALT -  - 15/4 , ALT -  - 13/3 , LONG - 4 - 9/1</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>I - TP5/20G - %75 / 32 işlem - ADAY (13g/-5/%56)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>36.35689926</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 2 - 1/21 , SHORT - 8 - 5/18 , SHORT - 8 - 7/16</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (13g/-2/%70)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>493.58499146</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+SHORT - 7 - 2/17 , SHORT - 8 - 3/16 , LONG - 1136 - 9/7</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/0/%50)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>370.69500732</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+SHORT - 34 - 10/1 , SHORT - 34 - 10/1 , SHORT - 34 - 9/1</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (8g/-7/%25)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>13.41499996</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+ALT -  - 13/2 , LONG - 34 - 6/4 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (8g/-1/%60)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>790.06011963</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 12 - 9/4 , LONG - 34 - 6/6 , SHORT - 8 - 5/5</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %85 / 48 işlem - ONAY (8g/-4/%33)
+H - TP2/10G - %77 / 73 işlem - ADAY (5g/-2/%53)
+S - TP5/20G - %63 / 48 işlem - ADAY (11g/-2/%43)
+Y - TP2/10G - %77 / 31 işlem - ADAY (8g/-4/%63)
+Y - TP5/20G - %70 / 23 işlem - ADAY (8g/-4/%60)
+Z - TP2/10G - %82 / 60 işlem - ADAY (8g/-4/%50)
+Z - TP5/20G - %65 / 51 işlem - ADAY (8g/-4/%63)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>360.99990845</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 23 - 7/4 , SHORT - 5 - 2/8 , SHORT - 7 - 7/4</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Q-TP5/10G, R-TP2/10G, R-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/10G - %60 / 25 işlem - ADAY (1g/+2/%100)
+R - TP2/10G - %81 / 42 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)
+Y - TP5/20G - %70 / 23 işlem - ADAY (2g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>215.88000488</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 1 - 2/20 , SHORT - 1 - 2/20 , SHORT - 1 - 0/9</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %81 / 26 işlem - ADAY (9g/-2/%17)
+T - TP5/20G - %86 / 28 işlem - ADAY (9g/-2/%50)
+U - TP5/20G - %60 / 155 işlem - ADAY (10g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 69 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>134.67500305</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+SHORT - 7 - 10/3 , SHORT - 7 - 10/3 , SHORT - 5 - 8/2</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (4g/-5/%65)
+S - TP5/20G - %63 / 48 işlem - ADAY (7g/-9/%65)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>928.85498047</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 46 - 5/7 , SHORT - 29 - 4/6 , SHORT - 63 - 5/5</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (6g/0/%100)
+U - TP5/20G - %60 / 155 işlem - ADAY (9g/-1/%80)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-1/%70)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>88.23999786</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 1 - 4/15 , LONG - 53 - 9/14 , SHORT - 18 - 7/6</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %82 / 60 işlem - ADAY (1g/-5/%95)
+Z - TP5/20G - %65 / 51 işlem - ADAY (1g/-5/%100)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>60.38029861</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 8 - 0/11 , LONG - 34 - 5/17 , UST -  - 1/13</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+4/%100)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>523.52001953</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+LONG - 34 - 19/12 , LONG - 34 - 15/10 , SHORT - 5 - 5/5</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (11g/-5/%50)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>35.09000015</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 11 - 10/14 , SHORT - 11 - 13/16 , SHORT - 5 - 7/5</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/20G - %63 / 48 işlem - ADAY (11g/-11/%43)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>53.29499817</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 5 - 0/9 , SHORT - 5 - 0/9 , SHORT - 5 - 0/9</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (8g/-4/%55)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>267.82470703</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 9 - 7/9 , LONG - 36 - 18/13 , SHORT - 8 - 6/4</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-4/%20)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>77.31999969</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 8 - 5/14 , SHORT - 8 - 5/14 , SHORT - 2 - 0/9</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-2/%35)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>27.54000092</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+SHORT - 1 - 1/14 , LONG - 51 - 3/16 , SHORT - 154 - 10/10</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (16g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>50.57500076</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2250,1672 +3983,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O27"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Hisse</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Düne_Göre_%</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Yarın_Alım</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Puan</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Onaylı_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Aday_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Toplam_Öneren_Sistem</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Kodları</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Detayı</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Neden</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Engel_Risk</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Son_Fiyat</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Fiyat_Tarihi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 19/1 , SHORT - 70 - 25/2 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (14g/-3/%40)
-I - TP5/20G - %75 / 32 işlem - ADAY (6g/-3/%77)
-Q - TP5/20G - %73 / 30 işlem - ADAY (2g/-4/%75)
-X - TP5/20G - %90 / 21 işlem - ADAY (14g/-3/%33)
-Y - TP5/20G - %70 / 23 işlem - ADAY (14g/-3/%44)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>346.29998779</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-LONG - 23 - 11/5 , SHORT - 6 - 2/8 , LONG - 9 - 8/2</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>X-TP2/10G, H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (8g/-2/%50)
-H - TP2/10G - %77 / 73 işlem - ADAY (5g/-1/%53)
-H - TP5/20G - %60 / 20 işlem - ADAY (5g/-1/%75)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 26 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>95.85500336</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX -1, TOPLAM 0, ALMA
-LONG - 2 - 15/2 , ALT -  - 13/0 , ALT -  - 13/0</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (6g/-2/%60)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>311.29998779</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 33 - 15/15 , SHORT - 20 - 6/10 , SHORT - 44 - 20/11</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/+2/%100)
-H - TP2/10G - %77 / 73 işlem - ADAY (1g/+2/%100)
-H - TP5/20G - %60 / 20 işlem - ADAY (1g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>385.82000732</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 32 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %81 / 26 işlem - ADAY (3g/-2/%60)
-T - TP5/20G - %86 / 28 işlem - ADAY (3g/-2/%75)
-Z - TP5/20G - %65 / 51 işlem - ADAY (6g/-2/%70)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 33 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>135.38999939</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WFC</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 44 - 5/7 , SHORT - 27 - 3/7 , SHORT - 61 - 4/6</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (4g/+1/%100)
-U - TP5/20G - %60 / 155 işlem - ADAY (7g/-1/%70)
-Z - TP5/20G - %65 / 51 işlem - ADAY (7g/-1/%65)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>88.58499908</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, NDX -1, TOPLAM -2, ALMA
-ALT -  - 13/2 , ALT -  - 12/1 , LONG - 2 - 8/3</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>I - TP5/20G - %75 / 32 işlem - ADAY (11g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>37.31999969</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 32 - 7/4 , SHORT - 32 - 7/4 , SHORT - 32 - 6/4</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (6g/-4/%60)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>13.89999962</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 3/13 , UST -  - 3/13 , SHORT - 14 - 4/5</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>89.08000183</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 6 - 2/17 , SHORT - 6 - 2/17 , SHORT - 10 - 4/5</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>575.82501221</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 2/23 , SHORT - 6 - 2/20 , SHORT - 6 - 3/19</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (11g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>505.23999023</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 2/16 , SHORT - 6 - 1/17 , LONG - 1134 - 7/9</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (15g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>376.20001221</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 13/2 , LONG - 32 - 8/3 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (6g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>785.51000977</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 10 - 8/4 , LONG - 32 - 6/6 , SHORT - 6 - 5/5</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (6g/-3/%56)
-H - TP2/10G - %77 / 73 işlem - ADAY (3g/-1/%85)
-S - TP5/20G - %63 / 48 işlem - ADAY (9g/-1/%59)
-Y - TP2/10G - %77 / 31 işlem - ADAY (6g/-3/%63)
-Y - TP5/20G - %70 / 23 işlem - ADAY (6g/-3/%75)
-Z - TP2/10G - %82 / 60 işlem - ADAY (6g/-3/%58)
-Z - TP5/20G - %65 / 51 işlem - ADAY (6g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>363.27999878</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 4/21 , UST -  - 2/23 , UST -  - 3/13</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %81 / 26 işlem - ADAY (7g/+1/%100)
-T - TP5/20G - %86 / 28 işlem - ADAY (7g/+1/%100)
-U - TP5/20G - %60 / 155 işlem - ADAY (8g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 69 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>138.71000671</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 5 - 12/0 , SHORT - 5 - 12/0 , SHORT - 3 - 10/0</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %77 / 73 işlem - ADAY (2g/-6/%70)
-S - TP5/20G - %63 / 48 işlem - ADAY (5g/-10/%75)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>919.3099975600001</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 3 - 6/6 , SHORT - 3 - 6/6 , SHORT - 1 - 4/8</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (4g/-3/%75)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>492.80999756</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-LONG - 32 - 19/12 , LONG - 32 - 16/9 , SHORT - 3 - 5/5</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-5/%70)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>34.95500183</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 9 - 9/15 , SHORT - 9 - 12/17 , SHORT - 3 - 6/6</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/20G - %63 / 48 işlem - ADAY (9g/-10/%59)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>53.97999954</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 0/10 , UST -  - 0/10 , UST -  - 0/10</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (6g/-4/%60)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>268.06500244</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-LONG - 37 - 10/19 , LONG - 34 - 13/16 , SHORT - 6 - 2/8</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>80.71499634</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 6 - 4/15 , SHORT - 6 - 4/15 , UST -  - 1/10</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/-1/%40)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>27.83499908</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 1/16 , LONG - 49 - 1/17 , SHORT - 152 - 8/12</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (14g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>51.31999969</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX -1, TOPLAM 0, ALMA
-UST -  - 2/12 , SHORT - 15 - 2/13 , UST -  - 1/10</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>166.17500305</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:O25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -580,12 +580,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
-ALT -  - 20/2 , LONG - 1 - 26/1 , ALT -  - 17/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 20/2 , LONG - 1 - 27/0 , ALT -  - 18/7</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
@@ -604,8 +604,8 @@
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %67 / 116 işlem - ADAY (16g/-5/%40)
-I - TP5/20G - %75 / 32 işlem - ADAY (8g/-4/%73)
-Q - TP5/20G - %73 / 30 işlem - ADAY (4g/-5/%64)
+I - TP5/20G - %75 / 32 işlem - ADAY (8g/-5/%73)
+Q - TP5/20G - %73 / 30 işlem - ADAY (4g/-6/%64)
 X - TP5/20G - %90 / 21 işlem - ADAY (16g/-5/%0)
 Y - TP5/20G - %70 / 23 işlem - ADAY (16g/-5/%38)</t>
         </is>
@@ -617,11 +617,11 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>341.67498779</v>
+        <v>339.51000977</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46281</v>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -648,44 +648,46 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, NDX +1, TOPLAM 4, İZLE
-ALT -  - 14/1 , ALT -  - 14/1 , ALT -  - 14/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 18/1 , ALT -  - 16/3 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (8g/-3/%30)</t>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (0g/0/%100)
+H - TP5/20G - %60 / 20 işlem - ADAY (0g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (8g/-5/%15)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>307.7250061</v>
+        <v>302.47000122</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46281</v>
@@ -694,11 +696,11 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.8</v>
+        <v>-2.9</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -712,8 +714,8 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
-SHORT - 39 - 15/2 , SHORT - 39 - 19/12 , SHORT - 46 - 22/10</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 35 - 16/1 , SHORT - 8 - 7/4 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -735,23 +737,23 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (3g/0/%100)
-H - TP2/10G - %77 / 73 işlem - ADAY (3g/0/%85)
-H - TP5/20G - %60 / 20 işlem - ADAY (3g/0/%63)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (7g/-5/%37)
+H - TP5/20G - %60 / 20 işlem - ADAY (7g/-5/%63)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>378.82998657</v>
+        <v>91.72000122</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46281</v>
@@ -760,11 +762,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -778,12 +780,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-LONG - 34 - 5/5 , LONG - 34 - 5/5 , LONG - 34 - 5/5</t>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+SHORT - 39 - 16/1 , SHORT - 39 - 21/11 , SHORT - 46 - 23/9</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0</v>
@@ -796,19 +798,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %81 / 26 işlem - ADAY (5g/-2/%38)
-T - TP5/20G - %86 / 28 işlem - ADAY (5g/-2/%50)
-Z - TP5/20G - %65 / 51 işlem - ADAY (8g/-2/%63)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (3g/-1/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (3g/-1/%85)
+H - TP5/20G - %60 / 20 işlem - ADAY (3g/-1/%63)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -817,7 +819,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>135.02999878</v>
+        <v>375.26000977</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46281</v>
@@ -826,62 +828,64 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
-SHORT - 20 - 12/17 , SHORT - 43 - 16/5 , SHORT - 3 - 7/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 34 - 7/3 , LONG - 34 - 7/3 , LONG - 34 - 7/3</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
+          <t>T - TP5/10G - %81 / 26 işlem - ADAY (5g/-4/%38)
+T - TP5/20G - %86 / 28 işlem - ADAY (5g/-4/%50)
+Z - TP5/20G - %65 / 51 işlem - ADAY (8g/-4/%63)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>58.36000061</v>
+        <v>132.94999695</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46281</v>
@@ -890,63 +894,62 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-1.3</v>
+        <v>-2.7</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 35 - 14/3 , SHORT - 8 - 5/5 , ALT -  - 11/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 20 - 13/16 , SHORT - 43 - 17/4 , SHORT - 3 - 8/4</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %77 / 73 işlem - ADAY (7g/-4/%37)
-H - TP5/20G - %60 / 20 işlem - ADAY (7g/-4/%63)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>93.29000092</v>
+        <v>57.90000153</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46281</v>
@@ -959,7 +962,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -973,8 +976,8 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
-LONG - 1 - 18/3 , LONG - 1 - 10/1 , ALT -  - 14/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 1 - 20/2 , ALT -  - 11/1 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -996,7 +999,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/+3/%100)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1010,7 +1013,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>317.36999512</v>
+        <v>312.8999939</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46281</v>
@@ -1023,7 +1026,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1037,8 +1040,8 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
-ALT -  - 15/4 , ALT -  - 13/3 , LONG - 4 - 9/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+ALT -  - 17/6 , ALT -  - 15/4 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1060,7 +1063,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>I - TP5/20G - %75 / 32 işlem - ADAY (13g/-5/%56)</t>
+          <t>I - TP5/20G - %75 / 32 işlem - ADAY (13g/-7/%56)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -1074,7 +1077,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>36.35689926</v>
+        <v>35.77999878</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46281</v>
@@ -1087,7 +1090,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1101,8 +1104,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 2 - 1/21 , SHORT - 8 - 5/18 , SHORT - 8 - 7/16</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 2 - 2/20 , SHORT - 8 - 5/17 , SHORT - 8 - 7/16</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1124,7 +1127,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (13g/-2/%70)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (13g/-3/%50)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1138,7 +1141,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>493.58499146</v>
+        <v>490.29998779</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46281</v>
@@ -1151,7 +1154,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1165,8 +1168,8 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
-SHORT - 7 - 2/17 , SHORT - 8 - 3/16 , LONG - 1136 - 9/7</t>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+SHORT - 7 - 1/17 , SHORT - 8 - 3/16 , LONG - 1136 - 9/7</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -1202,7 +1205,7 @@
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>370.69500732</v>
+        <v>370.92999268</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46281</v>
@@ -1215,7 +1218,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1229,8 +1232,8 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
-SHORT - 34 - 10/1 , SHORT - 34 - 10/1 , SHORT - 34 - 9/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 34 - 10/0 , SHORT - 34 - 10/0 , SHORT - 34 - 10/1</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1266,7 +1269,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>13.41499996</v>
+        <v>13.35000038</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46281</v>
@@ -1279,7 +1282,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1293,12 +1296,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
-ALT -  - 13/2 , LONG - 34 - 6/4 , ALT -  - 15/4</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 14/3 , LONG - 34 - 7/3 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>0</v>
@@ -1316,7 +1319,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (8g/-1/%60)</t>
+          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (8g/-2/%60)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1326,11 +1329,11 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>790.06011963</v>
+        <v>782.7199707</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46281</v>
@@ -1343,7 +1346,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1357,8 +1360,8 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
-LONG - 12 - 9/4 , LONG - 34 - 6/6 , SHORT - 8 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 8 - 4/6 , LONG - 34 - 7/5 , SHORT - 8 - 6/4</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1380,13 +1383,13 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (8g/-4/%33)
-H - TP2/10G - %77 / 73 işlem - ADAY (5g/-2/%53)
-S - TP5/20G - %63 / 48 işlem - ADAY (11g/-2/%43)
-Y - TP2/10G - %77 / 31 işlem - ADAY (8g/-4/%63)
-Y - TP5/20G - %70 / 23 işlem - ADAY (8g/-4/%60)
-Z - TP2/10G - %82 / 60 işlem - ADAY (8g/-4/%50)
-Z - TP5/20G - %65 / 51 işlem - ADAY (8g/-4/%63)</t>
+          <t>X - TP2/10G - %85 / 48 işlem - ONAY (8g/-5/%33)
+H - TP2/10G - %77 / 73 işlem - ADAY (5g/-3/%53)
+S - TP5/20G - %63 / 48 işlem - ADAY (11g/-3/%43)
+Y - TP2/10G - %77 / 31 işlem - ADAY (8g/-5/%63)
+Y - TP5/20G - %70 / 23 işlem - ADAY (8g/-5/%60)
+Z - TP2/10G - %82 / 60 işlem - ADAY (8g/-5/%50)
+Z - TP5/20G - %65 / 51 işlem - ADAY (8g/-5/%63)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1400,7 +1403,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>360.99990845</v>
+        <v>358.07998657</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46281</v>
@@ -1409,11 +1412,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.7</v>
+        <v>-6.1</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1427,47 +1430,46 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 23 - 7/4 , SHORT - 5 - 2/8 , SHORT - 7 - 7/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 1 - 3/19 , SHORT - 1 - 4/19 , SHORT - 1 - 2/8</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Q-TP5/10G, R-TP2/10G, R-TP5/20G, Y-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/10G - %60 / 25 işlem - ADAY (1g/+2/%100)
-R - TP2/10G - %81 / 42 işlem - ADAY (0g/0/%100)
-R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)
-Y - TP5/20G - %70 / 23 işlem - ADAY (2g/+2/%100)</t>
+          <t>T - TP5/10G - %81 / 26 işlem - ADAY (9g/-3/%17)
+T - TP5/20G - %86 / 28 işlem - ADAY (9g/-3/%50)
+U - TP5/20G - %60 / 155 işlem - ADAY (10g/-3/%55)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 69 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>215.88000488</v>
+        <v>132.53999329</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46281</v>
@@ -1476,11 +1478,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-4.6</v>
+        <v>-0.1</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1494,37 +1496,36 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
-SHORT - 1 - 2/20 , SHORT - 1 - 2/20 , SHORT - 1 - 0/9</t>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+SHORT - 7 - 10/3 , SHORT - 7 - 10/3 , SHORT - 5 - 9/2</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
+          <t>H-TP2/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %81 / 26 işlem - ADAY (9g/-2/%17)
-T - TP5/20G - %86 / 28 işlem - ADAY (9g/-2/%50)
-U - TP5/20G - %60 / 155 işlem - ADAY (10g/-1/%85)</t>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (4g/-5/%65)
+S - TP5/20G - %63 / 48 işlem - ADAY (7g/-9/%65)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 69 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1533,7 +1534,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>134.67500305</v>
+        <v>926.54998779</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46281</v>
@@ -1542,11 +1543,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.1</v>
+        <v>-3</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1560,8 +1561,8 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
-SHORT - 7 - 10/3 , SHORT - 7 - 10/3 , SHORT - 5 - 8/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 46 - 6/6 , SHORT - 29 - 5/5 , SHORT - 63 - 6/4</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1571,25 +1572,26 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>H-TP2/10G, S-TP5/20G</t>
+          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %77 / 73 işlem - ADAY (4g/-5/%65)
-S - TP5/20G - %63 / 48 işlem - ADAY (7g/-9/%65)</t>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (6g/-1/%67)
+U - TP5/20G - %60 / 155 işlem - ADAY (9g/-2/%65)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-2/%70)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1598,7 +1600,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>928.85498047</v>
+        <v>87.05000305</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46281</v>
@@ -1607,11 +1609,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-1.6</v>
+        <v>-6.5</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1625,37 +1627,36 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 46 - 5/7 , SHORT - 29 - 4/6 , SHORT - 63 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 1 - 6/13 , LONG - 53 - 11/13 , SHORT - 18 - 8/4</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (6g/0/%100)
-U - TP5/20G - %60 / 155 işlem - ADAY (9g/-1/%80)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-1/%70)</t>
+          <t>Z - TP2/10G - %82 / 60 işlem - ADAY (1g/-7/%95)
+Z - TP5/20G - %65 / 51 işlem - ADAY (1g/-7/%100)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -1664,7 +1665,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>88.23999786</v>
+        <v>59.36000061</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46281</v>
@@ -1673,11 +1674,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-4.9</v>
+        <v>0.8</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1691,45 +1692,46 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 1 - 4/15 , LONG - 53 - 9/14 , SHORT - 18 - 7/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 23 - 7/3 , SHORT - 5 - 3/7 , SHORT - 7 - 7/3</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %82 / 60 işlem - ADAY (1g/-5/%95)
-Z - TP5/20G - %65 / 51 işlem - ADAY (1g/-5/%100)</t>
+          <t>Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)
+Q - TP5/10G - %60 / 25 işlem - ADAY (1g/+1/%100)
+Y - TP5/20G - %70 / 23 işlem - ADAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 23 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>60.38029861</v>
+        <v>213.8999939</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46281</v>
@@ -1742,7 +1744,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1756,8 +1758,8 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-LONG - 8 - 0/11 , LONG - 34 - 5/17 , UST -  - 1/13</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 5 - 2/9 , LONG - 34 - 7/16 , SHORT - 3 - 1/11</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1779,7 +1781,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+4/%100)</t>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+1/%100)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1793,7 +1795,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>523.52001953</v>
+        <v>512.5</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46281</v>
@@ -1806,7 +1808,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-1.6</v>
+        <v>-3.3</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1820,8 +1822,8 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
-LONG - 34 - 19/12 , LONG - 34 - 15/10 , SHORT - 5 - 5/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 9 - 9/7 , SHORT - 9 - 8/4 , SHORT - 5 - 6/4</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1843,7 +1845,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (11g/-5/%50)</t>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (11g/-6/%50)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1857,7 +1859,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>35.09000015</v>
+        <v>34.50999832</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46281</v>
@@ -1870,7 +1872,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-1.7</v>
+        <v>-3.5</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1884,8 +1886,8 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 11 - 10/14 , SHORT - 11 - 13/16 , SHORT - 5 - 7/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 11 - 12/12 , SHORT - 11 - 15/15 , SHORT - 5 - 9/3</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1907,7 +1909,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/20G - %63 / 48 işlem - ADAY (11g/-11/%43)</t>
+          <t>S - TP5/20G - %63 / 48 işlem - ADAY (11g/-13/%43)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1921,7 +1923,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>53.29499817</v>
+        <v>52.29999924</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46281</v>
@@ -1934,7 +1936,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1948,8 +1950,8 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
-SHORT - 5 - 0/9 , SHORT - 5 - 0/9 , SHORT - 5 - 0/9</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 5 - 1/9 , SHORT - 5 - 1/9 , SHORT - 5 - 1/9</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1971,7 +1973,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (8g/-4/%55)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (8g/-4/%60)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1985,7 +1987,7 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>267.82470703</v>
+        <v>267.27999878</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46281</v>
@@ -1998,7 +2000,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2012,8 +2014,8 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
-SHORT - 9 - 7/9 , LONG - 36 - 18/13 , SHORT - 8 - 6/4</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 9 - 8/8 , LONG - 36 - 19/12 , SHORT - 8 - 8/3</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2035,7 +2037,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-4/%20)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-5/%5)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2049,7 +2051,7 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>77.31999969</v>
+        <v>76.41000366</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46281</v>
@@ -2062,7 +2064,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2076,8 +2078,8 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
-SHORT - 8 - 5/14 , SHORT - 8 - 5/14 , SHORT - 2 - 0/9</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 8 - 5/14 , SHORT - 8 - 5/14 , SHORT - 2 - 1/9</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2099,7 +2101,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-2/%35)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-3/%35)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2113,7 +2115,7 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>27.54000092</v>
+        <v>27.45999908</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46281</v>
@@ -2126,7 +2128,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-1.7</v>
+        <v>-3.3</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2140,8 +2142,8 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
-SHORT - 1 - 1/14 , LONG - 51 - 3/16 , SHORT - 154 - 10/10</t>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+SHORT - 1 - 2/13 , SHORT - 1 - 2/13 , SHORT - 154 - 11/9</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
@@ -2163,7 +2165,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (16g/+1/%100)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (16g/-1/%70)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2177,7 +2179,7 @@
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>50.57500076</v>
+        <v>49.75999832</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46281</v>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,6 +462,1688 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+LONG - 1 - 17/0 , ALT -  - 15/2 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G, Q-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (0g/0/%100)
+H - TP5/20G - %60 / 20 işlem - ADAY (1g/+1/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (9g/-4/%10)
+Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>304.29998779</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+LONG - 35 - 6/4 , LONG - 35 - 6/4 , LONG - 35 - 6/4</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+T - TP5/10G - %81 / 26 işlem - ADAY (6g/-3/%44)
+T - TP5/20G - %86 / 28 işlem - ADAY (6g/-3/%56)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%70)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>133.63000488</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+ALT -  - 16/5 , ALT -  - 14/3 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (14g/-7/%38)
+Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)
+Q - TP5/10G - %60 / 25 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 5 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>35.85499954</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 1 - 17/0 , LONG - 2 - 24/3 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (17g/-3/%45)
+I - TP5/20G - %75 / 32 işlem - ADAY (9g/-3/%70)
+Q - TP5/20G - %73 / 30 işlem - ADAY (5g/-4/%67)
+X - TP5/20G - %90 / 21 işlem - ADAY (17g/-3/%0)
+Y - TP5/20G - %70 / 23 işlem - ADAY (17g/-3/%38)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>348.1000061</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+SHORT - 40 - 15/2 , SHORT - 40 - 20/11 , SHORT - 47 - 22/10</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (4g/0/%95)
+H - TP2/10G - %77 / 73 işlem - ADAY (4g/0/%70)
+H - TP5/20G - %60 / 20 işlem - ADAY (4g/0/%63)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>377.95999146</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, NDX -1, TOPLAM 2, ALMA
+LONG - 2 - 18/4 , LONG - 1 - 9/1 , LONG - 1635 - 16/15</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (2g/+3/%100)
+R - TP2/10G - %81 / 42 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>317.20001221</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+ALT -  - 18/0 , SHORT - 139 - 19/6 , SHORT - 150 - 12/5</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 57 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>133.625</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+ALT -  - 13/1 , ALT -  - 13/1 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>199.72000122</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, NDX -1, TOPLAM 2, ALMA
+SHORT - 21 - 12/17 , SHORT - 21 - 13/7 , SHORT - 9 - 8/4</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/+1/%100)
+R - TP2/10G - %81 / 42 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 64 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>58.47499847</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX -1, TOPLAM -2, ALMA
+SHORT - 36 - 16/1 , SHORT - 9 - 7/3 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/0/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (8g/-6/%33)
+H - TP5/20G - %60 / 20 işlem - ADAY (8g/-6/%63)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>91.36000061</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+SHORT - 35 - 7/3 , SHORT - 35 - 7/3 , SHORT - 35 - 7/4</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-5/%45)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>13.72999954</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 8 - 2/17 , SHORT - 9 - 3/16 , LONG - 1137 - 8/8</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%50)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>370.92001343</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 3 - 1/21 , SHORT - 9 - 5/18 , SHORT - 9 - 6/16</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (14g/-2/%60)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>495.72750854</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+ALT -  - 11/0 , LONG - 35 - 5/5 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (9g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>800.85998535</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+LONG - 13 - 7/5 , LONG - 35 - 4/7 , SHORT - 9 - 3/6</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %85 / 48 işlem - ONAY (9g/-2/%25)
+H - TP2/10G - %77 / 73 işlem - ADAY (6g/0/%44)
+S - TP5/20G - %63 / 48 işlem - ADAY (12g/0/%36)
+Y - TP2/10G - %77 / 31 işlem - ADAY (9g/-2/%50)
+Y - TP5/20G - %70 / 23 işlem - ADAY (9g/-2/%69)
+Z - TP2/10G - %82 / 60 işlem - ADAY (9g/-2/%40)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-2/%70)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>367.73901367</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 2 - 4/18 , SHORT - 2 - 4/18 , SHORT - 2 - 3/7</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>T-TP5/20G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/20G - %86 / 28 işlem - ADAY (10g/-4/%43)
+U - TP5/20G - %60 / 155 işlem - ADAY (11g/-3/%40)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>131.80999756</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, NDX -1, TOPLAM -2, ALMA
+SHORT - 2 - 2/9 , SHORT - 30 - 5/5 , SHORT - 64 - 5/5</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/0/%63)
+U - TP5/20G - %60 / 155 işlem - ADAY (10g/-2/%70)
+Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-2/%53)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>87.58999634</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 2 - 7/13 , SHORT - 2 - 7/13 , SHORT - 19 - 9/3</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %82 / 60 işlem - ADAY (2g/-7/%95)
+Z - TP5/20G - %65 / 51 işlem - ADAY (2g/-7/%90)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>58.875</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 8 - 4/7 , SHORT - 8 - 4/7 , SHORT - 6 - 3/6</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (5g/0/%53)
+S - TP5/20G - %63 / 48 işlem - ADAY (8g/-4/%63)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>975.63201904</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 10 - 11/6 , SHORT - 10 - 10/2 , SHORT - 6 - 8/2</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-8/%47)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>33.92499924</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+SHORT - 24 - 5/5 , SHORT - 6 - 0/9 , SHORT - 8 - 5/5</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Q-TP5/10G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/10G - %60 / 25 işlem - ADAY (2g/+3/%100)
+Y - TP5/20G - %70 / 23 işlem - ADAY (3g/+4/%100)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 21 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>218.8999939</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 12 - 12/12 , SHORT - 12 - 16/15 , SHORT - 6 - 9/3</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/20G - %63 / 48 işlem - ADAY (12g/-13/%36)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>52.20999908</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 6 - 0/9 , SHORT - 6 - 0/9 , SHORT - 6 - 0/9</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-4/%65)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>268</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 2 - 5/11 , SHORT - 2 - 5/11 , SHORT - 155 - 14/7</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/-3/%30)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>48.625</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2187,1804 +3869,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O26"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Hisse</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Düne_Göre_%</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Yarın_Alım</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Puan</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Onaylı_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Aday_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Toplam_Öneren_Sistem</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Kodları</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Detayı</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Neden</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Engel_Risk</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Son_Fiyat</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Fiyat_Tarihi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-ALT -  - 21/3 , SHORT - 71 - 27/0 , ALT -  - 18/7</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (15g/-5/%40)
-I - TP5/20G - %75 / 32 işlem - ADAY (7g/-5/%77)
-Q - TP5/20G - %73 / 30 işlem - ADAY (3g/-6/%64)
-X - TP5/20G - %90 / 21 işlem - ADAY (15g/-5/%0)
-Y - TP5/20G - %70 / 23 işlem - ADAY (15g/-5/%38)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>339.95999146</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-LONG - 24 - 12/4 , SHORT - 7 - 3/7 , LONG - 10 - 9/1</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>X-TP2/10G, H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (9g/-3/%38)
-H - TP2/10G - %77 / 73 işlem - ADAY (6g/-2/%44)
-H - TP5/20G - %60 / 20 işlem - ADAY (6g/-2/%67)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 26 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>94.78289795000001</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 38 - 16/1 , SHORT - 21 - 8/8 , SHORT - 45 - 23/9</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (2g/-1/%100)
-H - TP2/10G - %77 / 73 işlem - ADAY (2g/-1/%85)
-H - TP5/20G - %60 / 20 işlem - ADAY (2g/-1/%70)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>376.96499634</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (7g/-4/%35)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>305.64001465</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-SHORT - 54 - 21/1 , ALT -  - 13/3 , LONG - 1633 - 20/11</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>309.48001099</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-LONG - 33 - 5/5 , LONG - 33 - 5/5 , LONG - 33 - 5/5</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %81 / 26 işlem - ADAY (4g/-2/%50)
-T - TP5/20G - %86 / 28 işlem - ADAY (4g/-2/%63)
-Z - TP5/20G - %65 / 51 işlem - ADAY (7g/-2/%65)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 33 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>135.11500549</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-ALT -  - 16/5 , ALT -  - 14/3 , LONG - 3 - 10/0</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>I - TP5/20G - %75 / 32 işlem - ADAY (12g/-6/%63)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>36.24509811</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 33 - 9/1 , SHORT - 33 - 9/1 , SHORT - 33 - 8/2</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (7g/-6/%35)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>13.56999969</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
-SHORT - 7 - 2/16 , SHORT - 7 - 3/16 , SHORT - 11 - 5/5</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/0/%35)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>572.79998779</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-UST -  - 0/22 , SHORT - 7 - 3/19 , SHORT - 7 - 5/18</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (12g/-1/%70)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>500.25500488</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 6 - 0/18 , SHORT - 7 - 1/17 , LONG - 1135 - 8/8</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (16g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>374.77999878</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-UST -  - 2/12 , UST -  - 2/12 , SHORT - 15 - 6/4</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/-1/%35)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>88.18000031</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, NDX 0, TOPLAM -1, ALMA
-ALT -  - 14/3 , LONG - 33 - 8/3 , ALT -  - 17/6</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (7g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>781.0599975600001</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-LONG - 11 - 9/3 , LONG - 33 - 7/5 , SHORT - 7 - 5/5</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (7g/-4/%50)
-H - TP2/10G - %77 / 73 işlem - ADAY (4g/-2/%70)
-S - TP5/20G - %63 / 48 işlem - ADAY (10g/-2/%50)
-Y - TP2/10G - %77 / 31 işlem - ADAY (7g/-4/%63)
-Y - TP5/20G - %70 / 23 işlem - ADAY (7g/-4/%75)
-Z - TP2/10G - %82 / 60 işlem - ADAY (7g/-4/%58)
-Z - TP5/20G - %65 / 51 işlem - ADAY (7g/-4/%65)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>361.1499939</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-UST -  - 3/23 , UST -  - 2/23 , UST -  - 4/13</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %81 / 26 işlem - ADAY (8g/+2/%100)
-T - TP5/20G - %86 / 28 işlem - ADAY (8g/+2/%100)
-U - TP5/20G - %60 / 155 işlem - ADAY (9g/+3/%100)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 69 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>140.38000488</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 6 - 11/2 , SHORT - 6 - 11/2 , SHORT - 4 - 9/1</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %77 / 73 işlem - ADAY (3g/-5/%65)
-S - TP5/20G - %63 / 48 işlem - ADAY (6g/-9/%71)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>924.03497314</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-SHORT - 22 - 9/2 , SHORT - 4 - 4/6 , LONG - 410 - 16/9</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/10G, Q-TP5/20G, Y-TP2/10G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)
-Q - TP5/10G - %60 / 25 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %73 / 30 işlem - ADAY (0g/0/%100)
-Y - TP2/10G - %77 / 31 işlem - ADAY (1g/0/%100)
-Y - TP5/20G - %70 / 23 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 24 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>211.94999695</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WFC</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-SHORT - 45 - 4/8 , SHORT - 28 - 3/7 , SHORT - 62 - 4/6</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (5g/+1/%100)
-U - TP5/20G - %60 / 155 işlem - ADAY (8g/0/%80)
-Z - TP5/20G - %65 / 51 işlem - ADAY (8g/0/%63)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>88.86000061</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 4 - 4/8 , SHORT - 4 - 4/8 , SHORT - 2 - 2/9</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (5g/-1/%70)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>503.07998657</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-LONG - 33 - 17/14 , LONG - 33 - 13/11 , SHORT - 4 - 3/7</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-3/%53)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>35.65999985</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-SHORT - 10 - 8/15 , SHORT - 10 - 11/18 , SHORT - 4 - 5/7</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/20G - %63 / 48 işlem - ADAY (10g/-10/%50)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>54.22999954</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
-SHORT - 4 - 1/8 , SHORT - 4 - 1/8 , SHORT - 4 - 1/8</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (7g/-5/%50)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>264.54998779</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-SHORT - 8 - 6/10 , LONG - 36 - 15/15 , SHORT - 7 - 5/5</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/-3/%30)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>78.02500153</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL +1, NDX 0, TOPLAM 0, ALMA
-SHORT - 7 - 5/14 , SHORT - 7 - 5/14 , SHORT - 1 - 0/9</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/-3/%35)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>27.53000069</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-UST -  - 1/16 , LONG - 50 - 1/17 , SHORT - 153 - 8/12</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (15g/+3/%100)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>51.49499893</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-UST -  - 4/13 , SHORT - 16 - 0/14 , UST -  - 2/11</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (19g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>168.69000244</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:O27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$32</definedName>
   </definedNames>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,11 +562,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -581,38 +581,37 @@
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 1 - 17/0 , ALT -  - 15/2 , ALT -  - 15/2</t>
+LONG - 35 - 7/3 , LONG - 35 - 7/3 , LONG - 35 - 7/3</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G, Q-TP2/10G</t>
+          <t>I-TP2/10G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
-H - TP2/10G - %77 / 73 işlem - ADAY (0g/0/%100)
-H - TP5/20G - %60 / 20 işlem - ADAY (1g/+1/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (9g/-4/%10)
-Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)</t>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+T - TP5/10G - %81 / 26 işlem - ADAY (6g/-4/%44)
+T - TP5/20G - %86 / 28 işlem - ADAY (6g/-4/%56)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-4/%70)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -621,7 +620,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>304.29998779</v>
+        <v>132.69999695</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46282</v>
@@ -630,11 +629,11 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -647,165 +646,29 @@
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 35 - 6/4 , LONG - 35 - 6/4 , LONG - 35 - 6/4</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-T - TP5/10G - %81 / 26 işlem - ADAY (6g/-3/%44)
-T - TP5/20G - %86 / 28 işlem - ADAY (6g/-3/%56)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 37 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>133.63000488</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 16/5 , ALT -  - 14/3 , LONG - 1 - 10/1</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (14g/-7/%38)
-Q - TP2/10G - %86 / 29 işlem - ADAY (0g/0/%100)
-Q - TP5/10G - %60 / 25 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %73 / 30 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 5 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>35.85499954</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
 LONG - 1 - 17/0 , LONG - 2 - 24/3 , ALT -  - 15/4</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %67 / 116 işlem - ADAY (17g/-3/%45)
 I - TP5/20G - %75 / 32 işlem - ADAY (9g/-3/%70)
@@ -814,18 +677,152 @@
 Y - TP5/20G - %70 / 23 işlem - ADAY (17g/-3/%38)</t>
         </is>
       </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>347.29998779</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+ALT -  - 18/0 , ALT -  - 16/3 , ALT -  - 16/3</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
+H - TP2/10G - %77 / 73 işlem - ADAY (0g/0/%100)
+H - TP5/20G - %60 / 20 işlem - ADAY (1g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (9g/-5/%10)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>302.51000977</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 40 - 16/1 , SHORT - 40 - 21/11 , SHORT - 47 - 23/9</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (4g/-1/%90)
+H - TP2/10G - %77 / 73 işlem - ADAY (4g/-1/%70)
+H - TP5/20G - %60 / 20 işlem - ADAY (4g/-1/%63)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>348.1000061</v>
+        <v>375.20999146</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46282</v>
@@ -834,65 +831,63 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 40 - 15/2 , SHORT - 40 - 20/11 , SHORT - 47 - 22/10</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+ALT -  - 18/0 , SHORT - 139 - 19/6 , SHORT - 150 - 12/5</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+          <t>E-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (4g/0/%95)
-H - TP2/10G - %77 / 73 işlem - ADAY (4g/0/%70)
-H - TP5/20G - %60 / 20 işlem - ADAY (4g/0/%63)
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
 I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>377.95999146</v>
+        <v>133.66000366</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46282</v>
@@ -901,11 +896,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -919,12 +914,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, NDX -1, TOPLAM 2, ALMA
-LONG - 2 - 18/4 , LONG - 1 - 9/1 , LONG - 1635 - 16/15</t>
+          <t>BIS 0, PHL 0, CNDL +1, NDX -1, TOPLAM 0, ALMA
+SHORT - 21 - 13/17 , SHORT - 21 - 14/7 , SHORT - 9 - 9/4</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>0</v>
@@ -937,19 +932,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (2g/+3/%100)
-R - TP2/10G - %81 / 42 işlem - ADAY (0g/0/%100)
-R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -958,7 +953,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>317.20001221</v>
+        <v>58.18000031</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46282</v>
@@ -967,26 +962,26 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , SHORT - 139 - 19/6 , SHORT - 150 - 12/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+LONG - 2 - 19/2 , LONG - 1 - 10/0 , LONG - 1635 - 17/14</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -996,34 +991,35 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP2/10G</t>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (2g/+2/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>133.625</v>
+        <v>313.47000122</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46282</v>
@@ -1036,7 +1032,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-1.1</v>
+        <v>-2.5</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1051,7 +1047,7 @@
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 13/1 , ALT -  - 13/1 , ALT -  - 14/3</t>
+ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1087,7 +1083,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>199.72000122</v>
+        <v>197</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46282</v>
@@ -1096,11 +1092,11 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>-1.6</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1114,45 +1110,46 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, NDX -1, TOPLAM 2, ALMA
-SHORT - 21 - 12/17 , SHORT - 21 - 13/7 , SHORT - 9 - 8/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+ALT -  - 18/0 , SHORT - 9 - 8/2 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP2/10G</t>
+          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/+1/%100)
-R - TP2/10G - %81 / 42 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/-2/%90)
+H - TP2/10G - %77 / 73 işlem - ADAY (8g/-7/%33)
+H - TP5/20G - %60 / 20 işlem - ADAY (8g/-7/%63)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 64 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>58.47499847</v>
+        <v>90.26999664</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46282</v>
@@ -1161,64 +1158,62 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX -1, TOPLAM -2, ALMA
-SHORT - 36 - 16/1 , SHORT - 9 - 7/3 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+ALT -  - 20/7 , ALT -  - 20/7 , ALT -  - 19/8</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/0/%100)
-H - TP2/10G - %77 / 73 işlem - ADAY (8g/-6/%33)
-H - TP5/20G - %60 / 20 işlem - ADAY (8g/-6/%63)</t>
+          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>91.36000061</v>
+        <v>248.47999573</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46282</v>
@@ -1227,11 +1222,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1246,11 +1241,11 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 35 - 7/3 , SHORT - 35 - 7/3 , SHORT - 35 - 7/4</t>
+ALT -  - 14/3 , ALT -  - 13/2 , LONG - 1 - 8/2</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0</v>
@@ -1263,17 +1258,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>I-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-5/%45)</t>
+          <t>I - TP5/20G - %75 / 32 işlem - ADAY (14g/-5/%38)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1282,7 +1277,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>13.72999954</v>
+        <v>36.36000061</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46282</v>
@@ -1291,11 +1286,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1309,8 +1304,8 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 8 - 2/17 , SHORT - 9 - 3/16 , LONG - 1137 - 8/8</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+SHORT - 35 - 8/2 , SHORT - 35 - 8/2 , SHORT - 35 - 8/3</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1332,7 +1327,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%50)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-6/%30)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1346,7 +1341,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>370.92001343</v>
+        <v>13.60999966</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46282</v>
@@ -1355,11 +1350,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1373,12 +1368,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 3 - 1/21 , SHORT - 9 - 5/18 , SHORT - 9 - 6/16</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 8 - 2/17 , SHORT - 9 - 3/16 , LONG - 1137 - 9/7</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -1396,7 +1391,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (14g/-2/%60)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%50)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1406,11 +1401,11 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>495.72750854</v>
+        <v>369.92999268</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46282</v>
@@ -1419,11 +1414,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1437,12 +1432,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 11/0 , LONG - 35 - 5/5 , ALT -  - 14/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 3 - 1/21 , SHORT - 9 - 4/18 , SHORT - 9 - 6/17</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>0</v>
@@ -1455,26 +1450,26 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (9g/0/%100)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (14g/-1/%70)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>800.85998535</v>
+        <v>497.75</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46282</v>
@@ -1483,133 +1478,132 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+ALT -  - 11/1 , LONG - 35 - 5/5 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (9g/0/%69)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>798.5700073199999</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="B17" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 13 - 7/5 , LONG - 35 - 4/7 , SHORT - 9 - 3/6</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
+LONG - 13 - 7/5 , LONG - 35 - 5/7 , SHORT - 9 - 4/6</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (9g/-2/%25)
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %85 / 48 işlem - ONAY (9g/-3/%25)
 H - TP2/10G - %77 / 73 işlem - ADAY (6g/0/%44)
 S - TP5/20G - %63 / 48 işlem - ADAY (12g/0/%36)
-Y - TP2/10G - %77 / 31 işlem - ADAY (9g/-2/%50)
-Y - TP5/20G - %70 / 23 işlem - ADAY (9g/-2/%69)
-Z - TP2/10G - %82 / 60 işlem - ADAY (9g/-2/%40)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-2/%70)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
+Y - TP2/10G - %77 / 31 işlem - ADAY (9g/-3/%50)
+Y - TP5/20G - %70 / 23 işlem - ADAY (9g/-3/%69)
+Z - TP2/10G - %82 / 60 işlem - ADAY (9g/-3/%40)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%70)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N16" s="7" t="n">
-        <v>367.73901367</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 4/18 , SHORT - 2 - 4/18 , SHORT - 2 - 3/7</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>T-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/20G - %86 / 28 işlem - ADAY (10g/-4/%43)
-U - TP5/20G - %60 / 155 işlem - ADAY (11g/-3/%40)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N17" s="7" t="n">
-        <v>131.80999756</v>
+        <v>366.20001221</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46282</v>
@@ -1618,11 +1612,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1636,46 +1630,45 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, NDX -1, TOPLAM -2, ALMA
-SHORT - 2 - 2/9 , SHORT - 30 - 5/5 , SHORT - 64 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 2 - 3/19 , SHORT - 2 - 3/19 , SHORT - 2 - 2/8</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+          <t>T-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/0/%63)
-U - TP5/20G - %60 / 155 işlem - ADAY (10g/-2/%70)
-Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-2/%53)</t>
+          <t>T - TP5/20G - %86 / 28 işlem - ADAY (10g/-3/%43)
+U - TP5/20G - %60 / 155 işlem - ADAY (11g/-2/%60)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>87.58999634</v>
+        <v>133.19000244</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46282</v>
@@ -1684,128 +1677,129 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 2 - 3/9 , SHORT - 30 - 5/5 , SHORT - 64 - 6/4</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/-1/%63)
+U - TP5/20G - %60 / 155 işlem - ADAY (10g/-3/%55)
+Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-3/%53)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>86.88999939</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>OXY</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="B20" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 2 - 7/13 , SHORT - 2 - 7/13 , SHORT - 19 - 9/3</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 2 - 6/13 , LONG - 54 - 11/12 , SHORT - 19 - 8/4</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %82 / 60 işlem - ADAY (2g/-7/%95)
 Z - TP5/20G - %65 / 51 işlem - ADAY (2g/-7/%90)</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>58.875</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 8 - 4/7 , SHORT - 8 - 4/7 , SHORT - 6 - 3/6</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %77 / 73 işlem - ADAY (5g/0/%53)
-S - TP5/20G - %63 / 48 işlem - ADAY (8g/-4/%63)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>975.63201904</v>
+        <v>59.29000092</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46282</v>
@@ -1814,11 +1808,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-1.7</v>
+        <v>5.5</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1832,8 +1826,8 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 10 - 11/6 , SHORT - 10 - 10/2 , SHORT - 6 - 8/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 8 - 4/8 , SHORT - 8 - 4/8 , SHORT - 6 - 3/7</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1843,33 +1837,34 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>H-TP2/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-8/%47)</t>
+          <t>H - TP2/10G - %77 / 73 işlem - ADAY (5g/0/%100)
+S - TP5/20G - %63 / 48 işlem - ADAY (8g/-4/%63)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>33.92499924</v>
+        <v>977.5</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46282</v>
@@ -1878,127 +1873,127 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 10 - 10/6 , SHORT - 10 - 10/3 , SHORT - 6 - 8/3</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-8/%47)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>34.02999878</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="B23" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
 SHORT - 24 - 5/5 , SHORT - 6 - 0/9 , SHORT - 8 - 5/5</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Q-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/10G - %60 / 25 işlem - ADAY (2g/+3/%100)
 Y - TP5/20G - %70 / 23 işlem - ADAY (3g/+4/%100)</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 21 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N22" s="7" t="n">
-        <v>218.8999939</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 12 - 12/12 , SHORT - 12 - 16/15 , SHORT - 6 - 9/3</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/20G - %63 / 48 işlem - ADAY (12g/-13/%36)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
       <c r="N23" s="7" t="n">
-        <v>52.20999908</v>
+        <v>219.33999634</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46282</v>
@@ -2007,11 +2002,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2025,8 +2020,8 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 6 - 0/9 , SHORT - 6 - 0/9 , SHORT - 6 - 0/9</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 12 - 13/12 , SHORT - 12 - 16/14 , SHORT - 6 - 10/3</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2043,26 +2038,26 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>S-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-4/%65)</t>
+          <t>S - TP5/20G - %63 / 48 işlem - ADAY (12g/-13/%36)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>268</v>
+        <v>52.08000183</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46282</v>
@@ -2071,11 +2066,11 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-2.3</v>
+        <v>1.1</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 5/11 , SHORT - 2 - 5/11 , SHORT - 155 - 14/7</t>
+UST -  - 0/10 , UST -  - 0/10 , UST -  - 0/10</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2112,7 +2107,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/-3/%30)</t>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-3/%65)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2126,14 +2121,78 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>48.625</v>
+        <v>270.22000122</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 2 - 6/10 , SHORT - 2 - 6/10 , SHORT - 155 - 14/7</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/-4/%15)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>48.33000183</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O25"/>
+  <autoFilter ref="A1:O26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -8,13 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,11 +560,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -580,38 +578,36 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 35 - 7/3 , LONG - 35 - 7/3 , LONG - 35 - 7/3</t>
+          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+LONG - 8 - 11/2 , LONG - 8 - 7/4 , -</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-TP2/10G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+          <t>X-TP2/10G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-T - TP5/10G - %78 / 27 işlem - ADAY (6g/-4/%44)
-T - TP5/20G - %86 / 28 işlem - ADAY (6g/-4/%56)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-4/%70)</t>
+          <t>X - TP2/10G - %90 / 48 işlem - ONAY (6g/-1/%40)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -620,20 +616,20 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>132.69999695</v>
+        <v>70.85500336</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -647,61 +643,62 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-LONG - 1 - 17/0 , LONG - 2 - 24/3 , ALT -  - 15/4</t>
+          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+SHORT - 23 - 13/16 , SHORT - 46 - 17/4 , SHORT - 11 - 9/3</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (17g/-3/%45)
-I - TP5/20G - %75 / 32 işlem - ADAY (9g/-3/%70)
-Q - TP5/20G - %73 / 30 işlem - ADAY (5g/-4/%67)
-X - TP5/20G - %90 / 21 işlem - ADAY (17g/-3/%0)
-Y - TP5/20G - %67 / 24 işlem - ADAY (17g/-3/%38)</t>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (3g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (1g/0/%100)
+R - TP2/10G - %81 / 43 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>347.29998779</v>
+        <v>57.95999908</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -715,60 +712,57 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , ALT -  - 16/3 , ALT -  - 16/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 1 - 12/1 , LONG - 1 - 11/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+          <t>X-TP2/10G</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (0g/0/%100)
-H - TP2/10G - %77 / 75 işlem - ADAY (0g/0/%100)
-H - TP5/20G - %60 / 20 işlem - ADAY (1g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (9g/-5/%10)</t>
+          <t>X - TP2/10G - %90 / 48 işlem - ONAY (9g/-5/%0)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>302.51000977</v>
+        <v>201.07499695</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -782,38 +776,41 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 40 - 16/1 , SHORT - 40 - 21/11 , SHORT - 47 - 23/9</t>
+          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+ALT -  - 30/2 , ALT -  - 11/1 , ALT -  - 19/6</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (4g/-1/%90)
-H - TP2/10G - %77 / 75 işlem - ADAY (4g/-1/%70)
-H - TP5/20G - %60 / 20 işlem - ADAY (4g/-1/%63)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/-1/%75)
+I - TP5/20G - %75 / 32 işlem - ADAY (2g/-1/%90)
+Q - TP2/10G - %86 / 29 işlem - ADAY (2g/-1/%70)
+Q - TP5/10G - %60 / 25 işlem - ADAY (2g/-1/%65)
+Q - TP5/20G - %73 / 30 işlem - ADAY (2g/-1/%85)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -822,85 +819,90 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>375.20999146</v>
+        <v>192</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , SHORT - 139 - 19/6 , SHORT - 150 - 12/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 62 - 20/11 , SHORT - 42 - 12/9 , SHORT - 24 - 9/2</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP2/10G</t>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (0g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+1/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (2g/+1/%100)
+Q - TP2/10G - %86 / 29 işlem - ADAY (2g/+1/%100)
+Q - TP5/10G - %60 / 25 işlem - ADAY (2g/+1/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (1g/+1/%100)
+R - TP2/10G - %81 / 43 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>133.66000366</v>
+        <v>204.96499634</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -914,319 +916,327 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX -1, TOPLAM 0, ALMA
-SHORT - 21 - 13/17 , SHORT - 21 - 14/7 , SHORT - 9 - 9/4</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 3 - 13/4 , LONG - 4 - 19/7 , LONG - 2 - 11/2</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (19g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (11g/+1/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (7g/0/%80)
+X - TP5/20G - %90 / 21 işlem - ADAY (19g/+1/%100)
+Y - TP5/20G - %67 / 24 işlem - ADAY (15g/-2/%36)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>360.79989624</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+ALT -  - 21/3 , ALT -  - 11/1 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/-4/%60)
+H - TP5/20G - %60 / 20 işlem - ADAY (10g/-9/%25)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/-3/%55)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>87.72709656000001</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 19/1 , ALT -  - 17/4 , ALT -  - 17/4</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (2g/-1/%95)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>298.4750061</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+ALT -  - 21/3 , SHORT - 141 - 23/4 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (2g/-3/%70)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>129.41070557</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SPGI</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 46 - 11/6 , SHORT - 10 - 9/4 , LONG - 144 - 18/13</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
 I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+S - TP5/20G - %65 / 43 işlem - ADAY (11g/-10/%30)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, S: %4 üzeri fiyat momentumu teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
-      <c r="N7" s="7" t="n">
-        <v>58.18000031</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 2 - 19/2 , LONG - 1 - 10/0 , LONG - 1635 - 17/14</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/+2/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>313.47000122</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>197</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , SHORT - 9 - 8/2 , ALT -  - 14/3</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/-2/%90)
-H - TP2/10G - %77 / 75 işlem - ADAY (8g/-7/%33)
-H - TP5/20G - %60 / 20 işlem - ADAY (8g/-7/%63)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>90.26999664</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 14/1 , SHORT - 81 - 16/1 , ALT -  - 13/0</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
       <c r="N11" s="7" t="n">
-        <v>893.9299926800001</v>
+        <v>406.48001099</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1240,35 +1250,37 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 14/3 , ALT -  - 13/2 , LONG - 1 - 8/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 10 - 3/12 , SHORT - 23 - 6/9 , SHORT - 39 - 6/4</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>I - TP5/20G - %75 / 32 işlem - ADAY (14g/-5/%38)</t>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (2g/0/%100)
+H - TP5/20G - %60 / 20 işlem - ADAY (2g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1277,20 +1289,20 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>36.36000061</v>
+        <v>351.01919556</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1304,57 +1316,60 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 11/1 , LONG - 35 - 5/5 , ALT -  - 14/3</t>
+          <t>BIS +2, PHL 0, CNDL +1, NDX 0, TOPLAM 3, İZLE
+LONG - 37 - 6/5 , LONG - 37 - 6/5 , LONG - 37 - 6/5</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>R-TP5/20G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %67 / 24 işlem - ADAY (9g/0/%69)</t>
+          <t>R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)
+T - TP5/10G - %78 / 27 işlem - ADAY (8g/-3/%50)
+T - TP5/20G - %86 / 28 işlem - ADAY (8g/-3/%75)
+Z - TP5/20G - %65 / 51 işlem - ADAY (11g/-3/%55)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 21 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>798.5700073199999</v>
+        <v>134.25500488</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1368,57 +1383,58 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX -1, TOPLAM 0, ALMA
-SHORT - 13 - 6/4 , SHORT - 27 - 12/8 , SHORT - 25 - 6/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 46 - 14/3 , SHORT - 46 - 16/5 , LONG - 40 - 8/2</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %60 / 25 işlem - ADAY (13g/-6/%55)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 18 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>251.19000244</v>
+        <v>312.58999634</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1432,62 +1448,58 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 13 - 7/5 , LONG - 35 - 5/7 , SHORT - 9 - 4/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 3 - 8/4 , SHORT - 42 - 17/4 , SHORT - 1619 - 20/11</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %77 / 75 işlem - ADAY (6g/0/%44)
-S - TP5/20G - %65 / 43 işlem - ADAY (12g/0/%36)
-Y - TP2/10G - %77 / 31 işlem - ADAY (9g/-3/%50)
-Y - TP5/20G - %67 / 24 işlem - ADAY (9g/-3/%69)
-Z - TP2/10G - %83 / 64 işlem - ADAY (9g/-3/%40)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%70)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/+1/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>366.20001221</v>
+        <v>950.95001221</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1501,12 +1513,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 3/19 , SHORT - 2 - 3/19 , SHORT - 2 - 2/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+ALT -  - 14/1 , SHORT - 83 - 16/1 , LONG - 1 - 13/0</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
@@ -1519,41 +1531,41 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>H-TP2/10G, T-TP5/20G, U-TP5/20G</t>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %77 / 75 işlem - ADAY (0g/0/%100)
-T - TP5/20G - %86 / 28 işlem - ADAY (10g/-3/%43)
-U - TP5/20G - %60 / 25 işlem - ADAY (19g/-1/%13)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (8g/-1/%90)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>133.19000244</v>
+        <v>896.1849975600001</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1567,12 +1579,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 6/13 , LONG - 54 - 11/12 , SHORT - 19 - 8/4</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 26/3 , ALT -  - 26/3 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
@@ -1585,40 +1597,40 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (2g/-7/%95)
-Z - TP5/20G - %65 / 51 işlem - ADAY (2g/-7/%90)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/-2/%95)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/-2/%80)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>59.29000092</v>
+        <v>167.86999512</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1632,58 +1644,59 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 8 - 4/8 , SHORT - 8 - 4/8 , SHORT - 6 - 3/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 3 - 23/3 , LONG - 7 - 13/7 , LONG - 1 - 12/1</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>H-TP2/10G, S-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %77 / 75 işlem - ADAY (5g/0/%100)
-S - TP5/20G - %65 / 43 işlem - ADAY (8g/-4/%50)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (7g/+3/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (16g/-3/%9)
+Q - TP5/20G - %73 / 30 işlem - ADAY (18g/-7/%5)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>977.5</v>
+        <v>129.77999878</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-1.4</v>
+        <v>1.3</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1697,12 +1710,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 10 - 10/6 , SHORT - 10 - 10/3 , SHORT - 6 - 8/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 17 - 18/3 , ALT -  - 14/1 , ALT -  - 13/3</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
@@ -1715,39 +1728,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>I-TP2/10G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-8/%47)</t>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>34.02999878</v>
+        <v>23.02499962</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1761,58 +1774,57 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 3/9 , SHORT - 30 - 5/5 , SHORT - 64 - 6/4</t>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+SHORT - 29 - 20/11 , SHORT - 23 - 18/7 , SHORT - 38 - 11/5</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>H-TP5/20G, Z-TP5/20G</t>
+          <t>I-TP2/10G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/-1/%63)
-Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-3/%53)</t>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>86.88999939</v>
+        <v>194.83000183</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1826,12 +1838,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 24 - 5/5 , SHORT - 6 - 0/9 , SHORT - 8 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+ALT -  - 14/3 , ALT -  - 12/1 , LONG - 3 - 7/3</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
@@ -1844,1780 +1856,1651 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Q-TP5/10G, Y-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/10G - %60 / 25 işlem - ADAY (2g/+3/%100)
-Y - TP5/20G - %67 / 24 işlem - ADAY (3g/+4/%100)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+2/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (16g/-6/%9)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>36.23500061</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 11 - 4/15 , SHORT - 11 - 4/15 , SHORT - 15 - 7/4</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %78 / 41 işlem - ADAY (6g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>564.47998047</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 37 - 3/12 , LONG - 37 - 0/9 , LONG - 37 - 1/11</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (9g/+1/%100)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>441.42001343</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+ALT -  - 13/0 , ALT -  - 14/1 , LONG - 5 - 7/3</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (15g/-5/%22)
+R - TP5/20G - %78 / 41 işlem - ADAY (10g/-1/%100)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 29 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>206.61999512</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 4 - 15/6 , LONG - 3 - 7/3 , LONG - 1637 - 14/16</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (14g/-4/%20)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>320.88000488</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+ALT -  - 18/7 , ALT -  - 20/6 , ALT -  - 19/8</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>248.42999268</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 42 - 16/1 , SHORT - 25 - 9/7 , SHORT - 49 - 23/9</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (6g/-1/%90)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 12 - 12/5 , LONG - 39 - 23/9 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>73.625</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 8 - 5/7 , LONG - 41 - 9/11 , LONG - 7 - 4/6</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (5g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>356.45001221</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 3 - 14/10 , LONG - 2 - 3/7 , LONG - 2 - 3/7</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>P-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>P - TP2/10G - %88 / 40 işlem - ONAY (9g/-6/%13)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>219.33999634</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46282</v>
+      <c r="N30" s="7" t="n">
+        <v>299.76998901</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 15 - 3/7 , SHORT - 29 - 9/11 , SHORT - 27 - 4/6</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 25 işlem - ADAY (15g/-3/%50)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 18 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>257.86499023</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 21 - 1/8 , LONG - 21 - 1/8 , UST -  - 2/12</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (17g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>202.74989319</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+UST -  - 3/17 , UST -  - 3/17 , UST -  - 5/16</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (12g/-1/%33)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>690.59997559</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, NDX 0, TOPLAM -1, ALMA
+UST -  - 3/29 , SHORT - 14 - 12/12 , SHORT - 2 - 1/8</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (15g/-5/%29)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>137.24499512</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 37 - 11/18 , LONG - 3 - 2/8 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, Q-TP5/20G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/+3/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (17g/-1/%55)
+Y - TP5/20G - %67 / 24 işlem - ADAY (17g/-1/%22)
+Z - TP2/10G - %83 / 64 işlem - ADAY (9g/-3/%10)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%65)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>182.63999939</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 4 - 8/15 , SHORT - 4 - 8/15 , SHORT - 4 - 7/4</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/20G - %86 / 28 işlem - ADAY (12g/-7/%40)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 25 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>127.55999756</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 4 - 4/11 , SHORT - 4 - 2/20 , UST -  - 1/10</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (2g/-2/%75)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>187.02000427</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+LONG - 41 - 12/5 , LONG - 39 - 18/13 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (5g/-8/%40)
+Z - TP5/20G - %65 / 51 işlem - ADAY (5g/-8/%50)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+UST -  - 1/10 , UST -  - 1/10 , UST -  - 1/10</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (1g/+1/%100)
+Z - TP5/20G - %65 / 51 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>398.6000061</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 4 - 10/10 , SHORT - 4 - 10/10 , SHORT - 21 - 12/1</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (4g/-10/%30)
+Z - TP5/20G - %65 / 51 işlem - ADAY (4g/-10/%50)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>57.13000107</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 15 - 4/7 , LONG - 37 - 3/9 , SHORT - 11 - 2/8</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>R-TP5/20G, S-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %78 / 41 işlem - ADAY (6g/+3/%100)
+S - TP5/20G - %65 / 43 işlem - ADAY (14g/+2/%100)
+Z - TP5/20G - %65 / 51 işlem - ADAY (11g/0/%75)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, S: %4 üzeri fiyat momentumu teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>374.79998779</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 1 - 16/5 , SHORT - 24 - 18/12 , -</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (18g/-17/%8)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>50.16949844</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, NDX 0, TOPLAM -3, ALMA
+UST -  - 1/11 , LONG - 37 - 8/20 , UST -  - 2/11</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/20G - %65 / 43 işlem - ADAY (10g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>1043.8449707</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 27 - 1/9 , LONG - 34 - 2/9 , UST -  - 0/10</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>338.42498779</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 12 - 13/4 , SHORT - 12 - 12/1 , SHORT - 8 - 10/1</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (14g/-10/%20)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>33.29000092</v>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 49 - 7/5 , SHORT - 32 - 6/4 , SHORT - 66 - 6/4</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (9g/-2/%33)
+Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-3/%55)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>86.52500153</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>46286</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Hisse</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Düne_Göre_%</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Yarın_Alım</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Puan</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Onaylı_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Aday_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Toplam_Öneren_Sistem</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Kodları</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Detayı</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Neden</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Engel_Risk</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Son_Fiyat</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Fiyat_Tarihi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 35 - 7/3 , LONG - 35 - 7/3 , LONG - 35 - 7/3</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-T - TP5/10G - %81 / 26 işlem - ADAY (6g/-4/%44)
-T - TP5/20G - %86 / 28 işlem - ADAY (6g/-4/%56)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 37 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>132.69999695</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-LONG - 1 - 17/0 , LONG - 2 - 24/3 , ALT -  - 15/4</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (17g/-3/%45)
-I - TP5/20G - %75 / 32 işlem - ADAY (9g/-3/%70)
-Q - TP5/20G - %73 / 30 işlem - ADAY (5g/-4/%67)
-X - TP5/20G - %90 / 21 işlem - ADAY (17g/-3/%0)
-Y - TP5/20G - %70 / 23 işlem - ADAY (17g/-3/%38)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 50 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>347.29998779</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , ALT -  - 16/3 , ALT -  - 16/3</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
-H - TP2/10G - %77 / 73 işlem - ADAY (0g/0/%100)
-H - TP5/20G - %60 / 20 işlem - ADAY (1g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (9g/-5/%10)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>302.51000977</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 40 - 16/1 , SHORT - 40 - 21/11 , SHORT - 47 - 23/9</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (4g/-1/%90)
-H - TP2/10G - %77 / 73 işlem - ADAY (4g/-1/%70)
-H - TP5/20G - %60 / 20 işlem - ADAY (4g/-1/%63)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>375.20999146</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , SHORT - 139 - 19/6 , SHORT - 150 - 12/5</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 57 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>133.66000366</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX -1, TOPLAM 0, ALMA
-SHORT - 21 - 13/17 , SHORT - 21 - 14/7 , SHORT - 9 - 9/4</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>58.18000031</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 2 - 19/2 , LONG - 1 - 10/0 , LONG - 1635 - 17/14</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (2g/+2/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>313.47000122</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>197</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 18/0 , SHORT - 9 - 8/2 , ALT -  - 14/3</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (1g/-2/%90)
-H - TP2/10G - %77 / 73 işlem - ADAY (8g/-7/%33)
-H - TP5/20G - %60 / 20 işlem - ADAY (8g/-7/%63)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 64 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>90.26999664</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MCD</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 20/7 , ALT -  - 20/7 , ALT -  - 19/8</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 116 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 47 hisse / 74 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>248.47999573</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 14/3 , ALT -  - 13/2 , LONG - 1 - 8/2</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>I - TP5/20G - %75 / 32 işlem - ADAY (14g/-5/%38)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 23 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>36.36000061</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 35 - 8/2 , SHORT - 35 - 8/2 , SHORT - 35 - 8/3</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-6/%30)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>13.60999966</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 8 - 2/17 , SHORT - 9 - 3/16 , LONG - 1137 - 9/7</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (18g/0/%50)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>369.92999268</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 3 - 1/21 , SHORT - 9 - 4/18 , SHORT - 9 - 6/17</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (14g/-1/%70)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>497.75</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 11/1 , LONG - 35 - 5/5 , ALT -  - 14/3</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %70 / 23 işlem - ADAY (9g/0/%69)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 20 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>798.5700073199999</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 13 - 7/5 , LONG - 35 - 5/7 , SHORT - 9 - 4/6</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>X-TP2/10G, H-TP2/10G, S-TP5/20G, Y-TP2/10G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %85 / 48 işlem - ONAY (9g/-3/%25)
-H - TP2/10G - %77 / 73 işlem - ADAY (6g/0/%44)
-S - TP5/20G - %63 / 48 işlem - ADAY (12g/0/%36)
-Y - TP2/10G - %77 / 31 işlem - ADAY (9g/-3/%50)
-Y - TP5/20G - %70 / 23 işlem - ADAY (9g/-3/%69)
-Z - TP2/10G - %82 / 60 işlem - ADAY (9g/-3/%40)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>366.20001221</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 3/19 , SHORT - 2 - 3/19 , SHORT - 2 - 2/8</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>T-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/20G - %86 / 28 işlem - ADAY (10g/-3/%43)
-U - TP5/20G - %60 / 155 işlem - ADAY (11g/-2/%60)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>133.19000244</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WFC</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 3/9 , SHORT - 30 - 5/5 , SHORT - 64 - 6/4</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>H-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/-1/%63)
-U - TP5/20G - %60 / 155 işlem - ADAY (10g/-3/%55)
-Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-3/%53)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 69 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>86.88999939</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OXY</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 6/13 , LONG - 54 - 11/12 , SHORT - 19 - 8/4</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %82 / 60 işlem - ADAY (2g/-7/%95)
-Z - TP5/20G - %65 / 51 işlem - ADAY (2g/-7/%90)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>59.29000092</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 8 - 4/8 , SHORT - 8 - 4/8 , SHORT - 6 - 3/7</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %77 / 73 işlem - ADAY (5g/0/%100)
-S - TP5/20G - %63 / 48 işlem - ADAY (8g/-4/%63)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>977.5</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 10 - 10/6 , SHORT - 10 - 10/3 , SHORT - 6 - 8/3</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-8/%47)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>34.02999878</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 24 - 5/5 , SHORT - 6 - 0/9 , SHORT - 8 - 5/5</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Q-TP5/10G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/10G - %60 / 25 işlem - ADAY (2g/+3/%100)
-Y - TP5/20G - %70 / 23 işlem - ADAY (3g/+4/%100)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 21 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>219.33999634</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 12 - 13/12 , SHORT - 12 - 16/14 , SHORT - 6 - 10/3</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/20G - %63 / 48 işlem - ADAY (12g/-13/%36)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>52.08000183</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 0/10 , UST -  - 0/10 , UST -  - 0/10</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (9g/-3/%65)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>270.22000122</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 2 - 6/10 , SHORT - 2 - 6/10 , SHORT - 155 - 14/7</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 155 işlem - ADAY (17g/-4/%15)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>48.33000183</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:O26"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -476,7 +476,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -578,36 +578,38 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
-LONG - 8 - 11/2 , LONG - 8 - 7/4 , -</t>
+          <t>BIS +2, PHL 0, CNDL +1, NDX 0, TOPLAM 3, İZLE
+LONG - 8 - 11/1 , LONG - 8 - 7/4 , -</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X-TP2/10G, I-TP2/10G</t>
+          <t>X-TP2/10G, I-TP2/10G, I-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>X - TP2/10G - %90 / 48 işlem - ONAY (6g/-1/%40)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -616,7 +618,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>70.85500336</v>
+        <v>70.83999634</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46286</v>
@@ -625,131 +627,129 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 1 - 12/1 , LONG - 1 - 11/2 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>X-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %90 / 48 işlem - ONAY (9g/-5/%0)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>201.1499939</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
 SHORT - 23 - 13/16 , SHORT - 46 - 17/4 , SHORT - 11 - 9/3</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
-E - TP5/20G - %67 / 118 işlem - ADAY (3g/0/%100)
+      <c r="F4" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, Q-TP5/20G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/0/%100)
 I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)
 Q - TP5/20G - %73 / 30 işlem - ADAY (1g/0/%100)
 R - TP2/10G - %81 / 43 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 50 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 52 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="N4" s="7" t="n">
         <v>57.95999908</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-LONG - 1 - 12/1 , LONG - 1 - 11/2 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>X-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>X - TP2/10G - %90 / 48 işlem - ONAY (9g/-5/%0)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 44 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>201.07499695</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46286</v>
@@ -758,11 +758,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.3</v>
+        <v>1.4</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -776,50 +776,48 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
-ALT -  - 30/2 , ALT -  - 11/1 , ALT -  - 19/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 3 - 12/5 , LONG - 4 - 18/7 , LONG - 2 - 11/2</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
-E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (2g/-1/%75)
-I - TP5/20G - %75 / 32 işlem - ADAY (2g/-1/%90)
-Q - TP2/10G - %86 / 29 işlem - ADAY (2g/-1/%70)
-Q - TP5/10G - %60 / 25 işlem - ADAY (2g/-1/%65)
-Q - TP5/20G - %73 / 30 işlem - ADAY (2g/-1/%85)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (19g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (11g/+2/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (7g/+1/%100)
+X - TP5/20G - %90 / 21 işlem - ADAY (19g/+1/%100)
+Y - TP5/20G - %67 / 24 işlem - ADAY (15g/-2/%36)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>192</v>
+        <v>362.66000366</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46286</v>
@@ -828,468 +826,468 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+ALT -  - 21/3 , ALT -  - 12/1 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/-4/%60)
+H - TP5/20G - %60 / 20 işlem - ADAY (10g/-9/%25)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/-3/%55)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>87.59999847</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+ALT -  - 20/2 , ALT -  - 17/4 , ALT -  - 17/4</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (2g/-2/%90)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>297.20001221</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
+ALT -  - 21/3 , SHORT - 141 - 22/4 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (2g/-3/%65)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>129.58999634</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SPGI</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 46 - 11/5 , SHORT - 10 - 9/3 , LONG - 144 - 18/13</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
+S - TP5/20G - %65 / 43 işlem - ADAY (11g/-10/%30)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, S: %4 üzeri fiyat momentumu teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>404.47000122</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+SHORT - 10 - 2/13 , SHORT - 23 - 6/10 , SHORT - 39 - 6/4</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (2g/+1/%100)
+H - TP5/20G - %60 / 20 işlem - ADAY (2g/+1/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>352.04000854</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+ALT -  - 31/3 , ALT -  - 12/1 , ALT -  - 20/6</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/-1/%90)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/-2/%75)
+I - TP5/20G - %75 / 32 işlem - ADAY (2g/-2/%90)
+Q - TP2/10G - %86 / 29 işlem - ADAY (2g/-2/%70)
+Q - TP5/10G - %60 / 25 işlem - ADAY (2g/-2/%65)
+Q - TP5/20G - %73 / 30 işlem - ADAY (2g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>190.97999573</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="B12" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-SHORT - 62 - 20/11 , SHORT - 42 - 12/9 , SHORT - 24 - 9/2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+1/%100)
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, NDX 0, TOPLAM -1, ALMA
+SHORT - 62 - 19/12 , SHORT - 42 - 11/9 , SHORT - 24 - 8/2</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+2/%100)
 I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)
 I - TP5/20G - %75 / 32 işlem - ADAY (2g/+1/%100)
 Q - TP2/10G - %86 / 29 işlem - ADAY (2g/+1/%100)
 Q - TP5/10G - %60 / 25 işlem - ADAY (2g/+1/%100)
-Q - TP5/20G - %73 / 30 işlem - ADAY (1g/+1/%100)
-R - TP2/10G - %81 / 43 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
+Q - TP5/20G - %73 / 30 işlem - ADAY (1g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>204.96499634</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-LONG - 3 - 13/4 , LONG - 4 - 19/7 , LONG - 2 - 11/2</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (19g/+1/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (11g/+1/%100)
-Q - TP5/20G - %73 / 30 işlem - ADAY (7g/0/%80)
-X - TP5/20G - %90 / 21 işlem - ADAY (19g/+1/%100)
-Y - TP5/20G - %67 / 24 işlem - ADAY (15g/-2/%36)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>360.79989624</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
-ALT -  - 21/3 , ALT -  - 11/1 , ALT -  - 17/6</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, H-TP5/20G, I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/-4/%60)
-H - TP5/20G - %60 / 20 işlem - ADAY (10g/-9/%25)
-I - TP2/10G - %78 / 123 işlem - ADAY (2g/-3/%55)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>87.72709656000001</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-ALT -  - 19/1 , ALT -  - 17/4 , ALT -  - 17/4</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
-E - TP5/20G - %67 / 118 işlem - ADAY (2g/-1/%95)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>298.4750061</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, NDX 0, TOPLAM 1, ALMA
-ALT -  - 21/3 , SHORT - 141 - 23/4 , ALT -  - 12/2</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
-E - TP5/20G - %67 / 118 işlem - ADAY (2g/-3/%70)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>129.41070557</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SPGI</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 46 - 11/6 , SHORT - 10 - 9/4 , LONG - 144 - 18/13</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP2/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)
-S - TP5/20G - %65 / 43 işlem - ADAY (11g/-10/%30)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, S: %4 üzeri fiyat momentumu teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>406.48001099</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 10 - 3/12 , SHORT - 23 - 6/9 , SHORT - 39 - 6/4</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %77 / 75 işlem - ADAY (2g/0/%100)
-H - TP5/20G - %60 / 20 işlem - ADAY (2g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (2g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
       <c r="N12" s="7" t="n">
-        <v>351.01919556</v>
+        <v>206.11999512</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46286</v>
@@ -1298,11 +1296,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1316,8 +1314,8 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, NDX 0, TOPLAM 3, İZLE
-LONG - 37 - 6/5 , LONG - 37 - 6/5 , LONG - 37 - 6/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 46 - 13/3 , SHORT - 46 - 15/6 , LONG - 40 - 8/3</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1327,27 +1325,25 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>R-TP5/20G, T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP2/10G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %78 / 41 işlem - ADAY (0g/0/%100)
-T - TP5/10G - %78 / 27 işlem - ADAY (8g/-3/%50)
-T - TP5/20G - %86 / 28 işlem - ADAY (8g/-3/%75)
-Z - TP5/20G - %65 / 51 işlem - ADAY (11g/-3/%55)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+1/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1356,7 +1352,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>134.25500488</v>
+        <v>313.58999634</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46286</v>
@@ -1365,11 +1361,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1384,7 +1380,7 @@
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 46 - 14/3 , SHORT - 46 - 16/5 , LONG - 40 - 8/2</t>
+ALT -  - 14/1 , SHORT - 83 - 16/1 , LONG - 1 - 12/0</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1394,34 +1390,35 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP2/10G</t>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (8g/0/%90)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>312.58999634</v>
+        <v>898.47998047</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46286</v>
@@ -1430,11 +1427,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1449,7 +1446,7 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-LONG - 3 - 8/4 , SHORT - 42 - 17/4 , SHORT - 1619 - 20/11</t>
+ALT -  - 25/2 , ALT -  - 25/2 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1471,22 +1468,22 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/+1/%100)
-I - TP2/10G - %78 / 123 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/-1/%95)
+I - TP2/10G - %78 / 123 işlem - ADAY (2g/-1/%80)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>950.95001221</v>
+        <v>168.52000427</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46286</v>
@@ -1495,11 +1492,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1513,8 +1510,8 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-ALT -  - 14/1 , SHORT - 83 - 16/1 , LONG - 1 - 13/0</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 3 - 22/4 , LONG - 7 - 12/8 , LONG - 1 - 11/2</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1531,28 +1528,28 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (8g/-1/%90)
-I - TP2/10G - %78 / 123 işlem - ADAY (2g/0/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (2g/0/%100)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (7g/+4/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (16g/-2/%9)
+Q - TP5/20G - %73 / 30 işlem - ADAY (18g/-6/%5)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>896.1849975600001</v>
+        <v>130.96000671</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46286</v>
@@ -1561,11 +1558,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1579,36 +1576,35 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-ALT -  - 26/3 , ALT -  - 26/3 , ALT -  - 17/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 17 - 19/3 , ALT -  - 15/2 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP2/10G</t>
+          <t>I-TP2/10G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/-2/%95)
-I - TP2/10G - %78 / 123 işlem - ADAY (2g/-2/%80)</t>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1617,7 +1613,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>167.86999512</v>
+        <v>22.93000031</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46286</v>
@@ -1626,11 +1622,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1644,46 +1640,44 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-LONG - 3 - 23/3 , LONG - 7 - 13/7 , LONG - 1 - 12/1</t>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+SHORT - 29 - 20/11 , SHORT - 23 - 18/7 , SHORT - 38 - 11/5</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>I-TP2/10G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (7g/+3/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (16g/-3/%9)
-Q - TP5/20G - %73 / 30 işlem - ADAY (18g/-7/%5)</t>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>129.77999878</v>
+        <v>194.33999634</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46286</v>
@@ -1692,11 +1686,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1711,34 +1705,35 @@
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 17 - 18/3 , ALT -  - 14/1 , ALT -  - 13/3</t>
+ALT -  - 14/3 , ALT -  - 13/2 , LONG - 3 - 8/2</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>E-TP5/20G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)</t>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+2/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (16g/-6/%9)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1747,7 +1742,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>23.02499962</v>
+        <v>36.09999847</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46286</v>
@@ -1756,7 +1751,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1774,12 +1769,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
-SHORT - 29 - 20/11 , SHORT - 23 - 18/7 , SHORT - 38 - 11/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 11 - 3/15 , SHORT - 11 - 3/15 , SHORT - 15 - 6/4</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
@@ -1792,17 +1787,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %78 / 123 işlem - ADAY (2g/+1/%100)</t>
+          <t>R - TP5/20G - %78 / 41 işlem - ADAY (6g/0/%85)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1811,7 +1806,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>194.83000183</v>
+        <v>567.65002441</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46286</v>
@@ -1820,11 +1815,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1838,36 +1833,37 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-ALT -  - 14/3 , ALT -  - 12/1 , LONG - 3 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 37 - 5/5 , LONG - 37 - 5/5 , LONG - 37 - 5/5</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+2/%100)
-I - TP5/20G - %75 / 32 işlem - ADAY (16g/-6/%9)</t>
+          <t>T - TP5/10G - %78 / 27 işlem - ADAY (8g/-2/%50)
+T - TP5/20G - %86 / 28 işlem - ADAY (8g/-2/%75)
+Z - TP5/20G - %65 / 51 işlem - ADAY (11g/-2/%65)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 34 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -1876,7 +1872,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>36.23500061</v>
+        <v>135.05000305</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46286</v>
@@ -1885,11 +1881,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1903,35 +1899,36 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 11 - 4/15 , SHORT - 11 - 4/15 , SHORT - 15 - 7/4</t>
+          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
+ALT -  - 13/0 , ALT -  - 14/1 , LONG - 5 - 7/3</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>H-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %78 / 41 işlem - ADAY (6g/-1/%85)</t>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (15g/-5/%22)
+R - TP5/20G - %78 / 41 işlem - ADAY (10g/-1/%100)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 29 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -1940,7 +1937,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>564.47998047</v>
+        <v>206.47999573</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46286</v>
@@ -1949,11 +1946,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1968,7 +1965,7 @@
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-LONG - 37 - 3/12 , LONG - 37 - 0/9 , LONG - 37 - 1/11</t>
+LONG - 4 - 16/5 , LONG - 3 - 7/3 , LONG - 1637 - 14/16</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1978,1065 +1975,1064 @@
         <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (14g/-5/%25)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>319.01000977</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, NDX 0, TOPLAM 3, İZLE
+LONG - 3 - 7/5 , SHORT - 42 - 16/5 , SHORT - 1619 - 19/12</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>959.39001465</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+ALT -  - 19/7 , ALT -  - 20/7 , ALT -  - 19/8</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>247.88000488</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 42 - 15/2 , SHORT - 25 - 8/8 , SHORT - 49 - 22/10</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (6g/0/%95)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>377.55999756</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 12 - 12/4 , LONG - 39 - 23/9 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>73.36000061</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 8 - 5/7 , SHORT - 33 - 4/11 , LONG - 7 - 4/6</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (5g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>354.97000122</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 3 - 13/11 , LONG - 2 - 2/7 , LONG - 2 - 2/7</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>P-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>P - TP2/10G - %88 / 40 işlem - ONAY (9g/-6/%13)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>302.27999878</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+SHORT - 15 - 3/7 , SHORT - 29 - 9/11 , SHORT - 27 - 3/7</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 25 işlem - ADAY (15g/-3/%50)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 18 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>258.45001221</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 21 - 0/9 , LONG - 21 - 0/9 , UST -  - 3/13</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (17g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>205.41999817</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+UST -  - 2/16 , UST -  - 2/16 , UST -  - 4/15</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (12g/-2/%33)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>684.72998047</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+UST -  - 4/29 , SHORT - 14 - 12/12 , SHORT - 2 - 1/9</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (15g/-5/%29)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>137.67999268</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 37 - 10/19 , LONG - 3 - 1/9 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, Q-TP5/20G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/+4/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (17g/0/%100)
+Y - TP5/20G - %67 / 24 işlem - ADAY (17g/0/%100)
+Z - TP2/10G - %83 / 64 işlem - ADAY (9g/-3/%20)
+Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%70)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>183.97000122</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 4 - 8/15 , SHORT - 4 - 8/15 , SHORT - 4 - 7/4</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/20G - %86 / 28 işlem - ADAY (12g/-7/%40)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 25 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>127.52999878</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 4 - 5/11 , SHORT - 4 - 3/19 , UST -  - 0/10</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (2g/-2/%60)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>186.11000061</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL +1, NDX 0, TOPLAM 2, ALMA
+LONG - 41 - 11/6 , LONG - 39 - 17/14 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (5g/-7/%40)
+Z - TP5/20G - %65 / 51 işlem - ADAY (5g/-7/%50)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>231.92999268</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+SHORT - 4 - 10/10 , SHORT - 4 - 10/10 , SHORT - 21 - 11/1</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (4g/-10/%30)
+Z - TP5/20G - %65 / 51 işlem - ADAY (4g/-10/%50)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
+LONG - 37 - 2/13 , UST -  - 1/10 , UST -  - 0/11</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %83 / 64 işlem - ADAY (9g/+1/%100)
 Z - TP5/20G - %65 / 51 işlem - ADAY (9g/+1/%100)</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>441.42001343</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX 0, TOPLAM 1, ALMA
-ALT -  - 13/0 , ALT -  - 14/1 , LONG - 5 - 7/3</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>H-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (15g/-5/%22)
-R - TP5/20G - %78 / 41 işlem - ADAY (10g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 29 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>206.61999512</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-LONG - 4 - 15/6 , LONG - 3 - 7/3 , LONG - 1637 - 14/16</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (14g/-4/%20)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>320.88000488</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MCD</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-ALT -  - 18/7 , ALT -  - 20/6 , ALT -  - 19/8</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>248.42999268</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 42 - 16/1 , SHORT - 25 - 9/7 , SHORT - 49 - 23/9</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (6g/-1/%90)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>374.5</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-SHORT - 12 - 12/5 , LONG - 39 - 23/9 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/+3/%100)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>73.625</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-LONG - 8 - 5/7 , LONG - 41 - 9/11 , LONG - 7 - 4/6</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (5g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>356.45001221</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-LONG - 3 - 14/10 , LONG - 2 - 3/7 , LONG - 2 - 3/7</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>P-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>P - TP2/10G - %88 / 40 işlem - ONAY (9g/-6/%13)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 33 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N30" s="7" t="n">
-        <v>299.76998901</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-SHORT - 15 - 3/7 , SHORT - 29 - 9/11 , SHORT - 27 - 4/6</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %60 / 25 işlem - ADAY (15g/-3/%50)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 18 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>257.86499023</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ANET</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-LONG - 21 - 1/8 , LONG - 21 - 1/8 , UST -  - 2/12</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %85 / 20 işlem - ADAY (17g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>202.74989319</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-UST -  - 3/17 , UST -  - 3/17 , UST -  - 5/16</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %85 / 20 işlem - ADAY (12g/-1/%33)</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="n">
-        <v>690.59997559</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, NDX 0, TOPLAM -1, ALMA
-UST -  - 3/29 , SHORT - 14 - 12/12 , SHORT - 2 - 1/8</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %85 / 20 işlem - ADAY (15g/-5/%29)</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="n">
-        <v>137.24499512</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-LONG - 37 - 11/18 , LONG - 3 - 2/8 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>H-TP5/20G, Q-TP5/20G, Y-TP5/20G, Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>H - TP5/20G - %60 / 20 işlem - ADAY (7g/+3/%100)
-Q - TP5/20G - %73 / 30 işlem - ADAY (17g/-1/%55)
-Y - TP5/20G - %67 / 24 işlem - ADAY (17g/-1/%22)
-Z - TP2/10G - %83 / 64 işlem - ADAY (9g/-3/%10)
-Z - TP5/20G - %65 / 51 işlem - ADAY (9g/-3/%65)</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="n">
-        <v>182.63999939</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-SHORT - 4 - 8/15 , SHORT - 4 - 8/15 , SHORT - 4 - 7/4</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/20G - %86 / 28 işlem - ADAY (12g/-7/%40)</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 25 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>127.55999756</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 4 - 4/11 , SHORT - 4 - 2/20 , UST -  - 1/10</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %77 / 75 işlem - ADAY (2g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="n">
-        <v>187.02000427</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
-LONG - 41 - 12/5 , LONG - 39 - 18/13 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (5g/-8/%40)
-Z - TP5/20G - %65 / 51 işlem - ADAY (5g/-8/%50)</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="n">
-        <v>229.5</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
-UST -  - 1/10 , UST -  - 1/10 , UST -  - 1/10</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (1g/+1/%100)
-Z - TP5/20G - %65 / 51 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N39" s="7" t="n">
-        <v>398.6000061</v>
+        <v>445.14001465</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46286</v>
@@ -3045,11 +3041,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-2.9</v>
+        <v>3</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3063,111 +3059,110 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX 0, TOPLAM 0, ALMA
-SHORT - 4 - 10/10 , SHORT - 4 - 10/10 , SHORT - 21 - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 15 - 4/8 , LONG - 37 - 3/9 , SHORT - 11 - 2/8</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>R-TP5/20G, S-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (4g/-10/%30)
-Z - TP5/20G - %65 / 51 işlem - ADAY (4g/-10/%50)</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="n">
-        <v>57.13000107</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-LONG - 15 - 4/7 , LONG - 37 - 3/9 , SHORT - 11 - 2/8</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>R-TP5/20G, S-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>R - TP5/20G - %78 / 41 işlem - ADAY (6g/+3/%100)
 S - TP5/20G - %65 / 43 işlem - ADAY (14g/+2/%100)
 Z - TP5/20G - %65 / 51 işlem - ADAY (11g/0/%75)</t>
         </is>
       </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, S: %4 üzeri fiyat momentumu teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>375.29998779</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+LONG - 1 - 16/5 , SHORT - 24 - 19/12 , -</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (18g/-17/%8)</t>
+        </is>
+      </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, S: %4 üzeri fiyat momentumu teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>374.79998779</v>
+        <v>50</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46286</v>
@@ -3176,11 +3171,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3194,8 +3189,8 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-LONG - 1 - 16/5 , SHORT - 24 - 18/12 , -</t>
+          <t>BIS -2, PHL 0, CNDL -1, NDX 0, TOPLAM -3, ALMA
+UST -  - 1/11 , LONG - 37 - 8/20 , UST -  - 2/11</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3212,26 +3207,26 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>S-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %85 / 20 işlem - ADAY (18g/-17/%8)</t>
+          <t>S - TP5/20G - %65 / 43 işlem - ADAY (10g/+3/%100)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>50.16949844</v>
+        <v>1043.95996094</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46286</v>
@@ -3240,11 +3235,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3258,8 +3253,8 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, NDX 0, TOPLAM -3, ALMA
-UST -  - 1/11 , LONG - 37 - 8/20 , UST -  - 2/11</t>
+          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
+LONG - 27 - 0/9 , LONG - 34 - 2/9 , UST -  - 0/10</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3276,26 +3271,26 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>S-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/20G - %65 / 43 işlem - ADAY (10g/+3/%100)</t>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+2/%100)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>1043.8449707</v>
+        <v>338.98001099</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46286</v>
@@ -3304,11 +3299,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0.7</v>
+        <v>-0.7</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3322,8 +3317,8 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX 0, TOPLAM 2, ALMA
-LONG - 27 - 1/9 , LONG - 34 - 2/9 , UST -  - 0/10</t>
+          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
+SHORT - 12 - 12/4 , SHORT - 12 - 12/1 , SHORT - 8 - 10/1</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3345,7 +3340,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+2/%100)</t>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (14g/-9/%25)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3355,11 +3350,11 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>338.42498779</v>
+        <v>33.38999939</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46286</v>
@@ -3368,11 +3363,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1</v>
+        <v>2.1</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3386,8 +3381,8 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX 0, TOPLAM -2, ALMA
-SHORT - 12 - 13/4 , SHORT - 12 - 12/1 , SHORT - 8 - 10/1</t>
+          <t>BIS -1, PHL 0, CNDL 0, NDX 0, TOPLAM -1, ALMA
+UST -  - 2/11 , UST -  - 2/11 , UST -  - 1/11</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -3409,7 +3404,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (14g/-10/%20)</t>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -3419,11 +3414,11 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>33.29000092</v>
+        <v>401.6499939</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46286</v>
@@ -3488,7 +3483,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>86.52500153</v>
+        <v>86.54000092</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46286</v>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,6 +462,3247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 9 - 12/1 , LONG - 9 - 7/3 , -</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>X-TP2/10G, I-TP2/10G, I-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>X - TP2/10G - %90 / 48 işlem - ONAY (7g/-2/%20)
+I - TP2/10G - %78 / 123 işlem - ADAY (1g/-1/%95)
+I - TP5/20G - %75 / 32 işlem - ADAY (1g/-1/%100)
+R - TP5/20G - %78 / 41 işlem - ADAY (1g/-1/%90)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>70.33000183</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 24 - 16/14 , SHORT - 47 - 19/2 , SHORT - 12 - 12/1</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, Q-TP5/20G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (4g/-2/%75)
+I - TP2/10G - %78 / 123 işlem - ADAY (1g/-2/%80)
+Q - TP5/20G - %73 / 30 işlem - ADAY (2g/-2/%75)
+R - TP2/10G - %81 / 43 işlem - ADAY (2g/-2/%65)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 52 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>56.52500153</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 63 - 23/9 , SHORT - 43 - 14/7 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (2g/-1/%95)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/-2/%65)
+I - TP5/20G - %75 / 32 işlem - ADAY (3g/-2/%95)
+Q - TP2/10G - %86 / 29 işlem - ADAY (3g/-2/%60)
+Q - TP5/10G - %60 / 25 işlem - ADAY (3g/-2/%55)
+Q - TP5/20G - %73 / 30 işlem - ADAY (2g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>200.41000366</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 2 - 17/5 , SHORT - 25 - 19/12 , -</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (0g/0/%100)
+P - TP5/20G - %85 / 20 işlem - ADAY (19g/-17/%15)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 63 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>49.72999954</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 8 - 12/8 , LONG - 8 - 12/8 , LONG - 2 - 11/2</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (8g/+3/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (17g/-3/%15)
+Q - TP5/20G - %73 / 30 işlem - ADAY (19g/-6/%0)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>130.6000061</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, NDX +1, TOPLAM 2, ALMA
+ALT -  - 13/0 , SHORT - 84 - 15/2 , LONG - 2 - 12/1</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (9g/0/%80)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (3g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>901.01000977</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+ALT -  - 14/3 , ALT -  - 12/2 , LONG - 4 - 8/3</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (0g/0/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (2g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (17g/-6/%15)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>36.01499939</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, NDX +1, TOPLAM 4, İZLE
+ALT -  - 17/0 , ALT -  - 15/2 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (1g/+2/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (3g/0/%95)
+I - TP2/10G - %78 / 123 işlem - ADAY (1g/+2/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (1g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>301.93499756</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, NDX +1, TOPLAM 2, ALMA
+ALT -  - 19/2 , SHORT - 142 - 21/5 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 84 işlem - ADAY (1g/+1/%100)
+E - TP5/20G - %67 / 118 işlem - ADAY (3g/-2/%80)
+I - TP2/10G - %78 / 123 işlem - ADAY (1g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>131.13000488</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SPGI</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+SHORT - 47 - 11/5 , SHORT - 11 - 9/3 , LONG - 145 - 18/13</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (1g/0/%90)
+S - TP5/20G - %65 / 43 işlem - ADAY (12g/-10/%25)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>404.2749939</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+SHORT - 11 - 6/10 , SHORT - 24 - 10/6 , SHORT - 40 - 9/1</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (3g/-3/%55)
+H - TP5/20G - %60 / 20 işlem - ADAY (3g/-3/%50)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/-3/%55)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>340.07998657</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, NDX +1, TOPLAM 0, ALMA
+ALT -  - 20/8 , LONG - 1 - 9/1 , ALT -  - 17/4</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/+1/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/0/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (3g/0/%100)
+Q - TP2/10G - %86 / 29 işlem - ADAY (3g/0/%100)
+Q - TP5/10G - %60 / 25 işlem - ADAY (3g/0/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (3g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>194.88499451</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+SHORT - 30 - 23/9 , SHORT - 24 - 20/5 , SHORT - 39 - 13/4</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (0g/0/%100)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/-2/%60)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>190.46000671</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+UST -  - 2/20 , UST -  - 2/20 , UST -  - 6/15</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (1g/+1/%100)
+I - TP5/20G - %75 / 32 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>266.05999756</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+SHORT - 47 - 15/2 , SHORT - 47 - 18/4 , LONG - 41 - 9/1</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/-1/%95)
+I - TP2/10G - %78 / 123 işlem - ADAY (1g/-2/%75)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>307.69711304</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+ALT -  - 23/1 , ALT -  - 12/1 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, H-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (4g/-5/%65)
+H - TP5/20G - %60 / 20 işlem - ADAY (11g/-9/%33)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/-3/%50)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>87.55000305</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 18 - 20/2 , ALT -  - 16/3 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (3g/-1/%65)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>22.62319946</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+UST -  - 9/29 , SHORT - 1 - 1/8 , SHORT - 1 - 1/9</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/20G, P-TP5/10G, P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (0g/0/%100)
+H - TP5/20G - %60 / 20 işlem - ADAY (0g/0/%100)
+P - TP5/10G - %81 / 21 işlem - ADAY (1g/-1/%80)
+P - TP5/20G - %85 / 20 işlem - ADAY (1g/-1/%100)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, P: %3-%6 kontrollü momentum ve çoklu teyit; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>40.59000015</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 12 - 5/14 , SHORT - 12 - 6/14 , SHORT - 16 - 8/3</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %78 / 41 işlem - ADAY (7g/-2/%85)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>558.59997559</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+ALT -  - 30/6 , ALT -  - 30/6 , ALT -  - 21/10</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/-5/%55)
+I - TP2/10G - %78 / 123 işlem - ADAY (3g/-5/%40)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>161.61000061</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+SHORT - 38 - 11/1 , ALT -  - 12/1 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (1g/-1/%95)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>13.07999992</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SYK</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+ALT -  - 23/1 , ALT -  - 23/1 , ALT -  - 18/7</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %78 / 123 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>276.91500854</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 4 - 12/5 , LONG - 5 - 18/7 , LONG - 3 - 10/2</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>I-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>I - TP5/20G - %75 / 32 işlem - ADAY (12g/+1/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (8g/0/%100)
+Y - TP5/20G - %67 / 24 işlem - ADAY (16g/-2/%22)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 24 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>362.42999268</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+SHORT - 5 - 10/10 , SHORT - 5 - 10/10 , SHORT - 22 - 11/1</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (5g/-10/%40)
+Z - TP5/20G - %65 / 51 işlem - ADAY (5g/-10/%50)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>57.13000107</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 2 - 10/3 , LONG - 1 - 11/2 , LONG - 6 - 4/6</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (16g/-3/%30)
+R - TP5/20G - %78 / 41 işlem - ADAY (11g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 29 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>211.27000427</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 5 - 16/5 , LONG - 4 - 7/3 , LONG - 1638 - 14/16</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (15g/-5/%25)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>318.17001343</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 4 - 8/5 , SHORT - 43 - 17/4 , SHORT - 1620 - 20/12</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (4g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>949.08001709</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+ALT -  - 17/6 , ALT -  - 19/5 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (3g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>251.16000366</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+ALT -  - 19/1 , ALT -  - 19/1 , SHORT - 145 - 26/7</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>79.71499634</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 13 - 14/3 , LONG - 41 - 23/9 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (2g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>72.07499695</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 43 - 16/1 , SHORT - 43 - 21/11 , SHORT - 50 - 23/9</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %67 / 118 işlem - ADAY (7g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 76 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>374.23999023</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+LONG - 38 - 7/3 , LONG - 38 - 7/3 , LONG - 38 - 7/3</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %78 / 27 işlem - ADAY (9g/-4/%15)
+T - TP5/20G - %86 / 28 işlem - ADAY (9g/-4/%60)
+Z - TP5/20G - %65 / 51 işlem - ADAY (12g/-4/%50)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 34 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>132.02999878</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 50 - 11/2 , SHORT - 33 - 9/1 , SHORT - 67 - 10/1</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (10g/-5/%25)
+Z - TP5/20G - %65 / 51 işlem - ADAY (13g/-6/%20)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>83.62010193</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, NDX +1, TOPLAM 0, ALMA
+SHORT - 16 - 5/5 , SHORT - 35 - 16/14 , SHORT - 28 - 5/5</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %60 / 25 işlem - ADAY (16g/-5/%50)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 18 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>254.39030457</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 5 - 9/15 , SHORT - 5 - 9/14 , SHORT - 5 - 7/3</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/20G - %86 / 28 işlem - ADAY (13g/-8/%35)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 25 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>126.77999878</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, NDX +1, TOPLAM 2, ALMA
+LONG - 22 - 1/8 , LONG - 22 - 1/8 , UST -  - 3/12</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (18g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>204.41999817</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+UST -  - 3/17 , UST -  - 2/11 , UST -  - 5/16</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (13g/-1/%29)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>693.4400024399999</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, NDX +1, TOPLAM 2, ALMA
+UST -  - 2/28 , SHORT - 15 - 13/11 , SHORT - 3 - 2/7</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %85 / 20 işlem - ADAY (16g/-6/%21)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 20 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>136.16000366</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+UST -  - 6/20 , UST -  - 6/20 , UST -  - 10/20</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>P-TP5/10G, P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/10G - %81 / 21 işlem - ADAY (1g/+2/%100)
+P - TP5/20G - %85 / 20 işlem - ADAY (1g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 21 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>262.26000977</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 5 - 7/9 , SHORT - 5 - 4/18 , SHORT - 1 - 2/8</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %77 / 75 işlem - ADAY (3g/-3/%50)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 31 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>183.71499634</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 16 - 4/8 , LONG - 32 - 5/18 , SHORT - 12 - 2/8</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>R-TP5/20G, S-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %78 / 41 işlem - ADAY (7g/+3/%100)
+S - TP5/20G - %65 / 43 işlem - ADAY (15g/+2/%100)
+Z - TP5/20G - %65 / 51 işlem - ADAY (12g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, S: %4 üzeri fiyat momentumu teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>376.90499878</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+LONG - 42 - 10/6 , LONG - 40 - 17/14 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %83 / 64 işlem - ADAY (6g/-7/%20)
+Z - TP5/20G - %65 / 51 işlem - ADAY (6g/-7/%40)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 38 - 10/19 , LONG - 4 - 1/9 , LONG - 4 - 0/9</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>H-TP5/20G, Q-TP5/20G, Y-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>H - TP5/20G - %60 / 20 işlem - ADAY (8g/+4/%100)
+Q - TP5/20G - %73 / 30 işlem - ADAY (18g/+1/%100)
+Y - TP5/20G - %67 / 24 işlem - ADAY (18g/+1/%100)
+Z - TP5/20G - %65 / 51 işlem - ADAY (10g/-2/%70)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 31 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>184.92999268</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+UST -  - 0/10 , LONG - 35 - 2/10 , UST -  - 1/10</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (7g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>342.49099731</v>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, NDX +1, TOPLAM 2, ALMA
+LONG - 9 - 6/6 , SHORT - 34 - 5/10 , LONG - 8 - 5/5</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (6g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>352.1000061</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+SHORT - 13 - 15/6 , SHORT - 13 - 12/1 , SHORT - 9 - 10/1</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (15g/-10/%15)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>33.27000046</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+UST -  - 1/11 , UST -  - 1/11 , UST -  - 2/11</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (2g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>402.39001465</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+LONG - 38 - 2/13 , UST -  - 1/10 , UST -  - 0/12</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %65 / 51 işlem - ADAY (10g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>446.66500854</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O49"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3495,7 +6738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$Q$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dün'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$Q$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dün'!$A$1:$Q$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$AS$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,6 +472,2088 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>SECIM</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>SECIM (kar/DD)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 65 - 25/8 , SHORT - 45 - 16/5 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>L5(13) %86
+MULTI(1) %90
+UVP(1) %100
+UBND(1) %88</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-3.57% / -3.08%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, A-TP2/10G, D1_DC05-TP2/10G, D2_DC05-TP2/10G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (5g/-4/%60)
+A - TP2/10G - %84 / 32 işlem - ADAY (5g/-4/%50)
+D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (5g/-4/%55)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (5g/-4/%55)
+E - TP2/10G - %81 / 147 işlem - ADAY (5g/-4/%50)</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY A: CNDL_GECIKMIS, D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga, E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 114 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>196.25999451</v>
+      </c>
+      <c r="Q2" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 6 - 15/2 , LONG - 7 - 22/4 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>UFLO(1) %83</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-4.94% / -4.35%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>D-TP5/20G, D2_DU03-TP5/20G, D3_NT03-TP5/20G, D3_NU02-TP5/20G, E-TP2/10G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>D - TP5/20G - %76 / 17 işlem - ADAY (11g/-4/%88)
+D2_DU03 - TP5/20G - %80 / 44 işlem - ADAY (18g/-5/%25)
+D3_NT03 - TP5/20G - %87 / 15 işlem - ADAY (11g/-4/%67)
+D3_NU02 - TP5/20G - %81 / 37 işlem - ADAY (19g/-6/%33)
+E - TP2/10G - %81 / 147 işlem - ADAY (0g/0/%100)
+Y - TP5/20G - %80 / 49 işlem - ADAY (18g/-5/%30)</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D: TDA_GERI_CEKILME, D2_DU03: V2 | Yeni SIS icin TDA teyidi ve ATL risk elemesi, D3_NT03: V3 | BIS ayrismasi biterken TDA gucleniyor, D3_NU02: V3 | TDA iki raporda guclenirken yeni CNDL LONG, E: PFY_GORECELI_UCUZ, Y: COKLU_TEYIT; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>349.92498779</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 2 - 12/0 , ALT -  - 16/5 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>L5(1) %88</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-2.65% / -3.45%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>V-TP5/20G, D1_DC05-TP2/10G, D2_DC05-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>V - TP5/20G - %89 / 27 işlem - ONAY (15g/-5/%75)
+D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (3g/-2/%65)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (3g/-2/%65)</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY V: MIRAS_WMA_TEYITLI; ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 140 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+ALT -  - 24/12 , ALT -  - 12/1 , ALT -  - 21/7</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP2/10G, Q-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (5g/-3/%65)
+E - TP2/10G - %81 / 147 işlem - ADAY (5g/-3/%50)
+Q - TP2/10G - %77 / 92 işlem - ADAY (5g/-3/%65)</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ, Q: CNDL_GECIKMIS_GORECELI_GERI_KALAN; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 68 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>188.16999817</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+ALT -  - 13/1 , SHORT - 86 - 16/2 , LONG - 4 - 12/1</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>C2(1) %94
+C4(1) %89</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.56% / -3.15%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, D3_NU01-TP2/10G, G-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (5g/0/%100)
+D3_NU01 - TP2/10G - %77 / 31 işlem - ADAY (8g/-2/%56)
+G - TP2/10G - %78 / 223 işlem - ADAY (9g/-1/%25)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY D3_NU01: V3 | Uzun WMA LONG icinde kisa WMA yeniden giris, G: PHL_KALITE_LAG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 89 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>897.92840576</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+UST -  - 1/19 , UST -  - 1/19 , UST -  - 5/14</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N16(1) %100
+L5(2) %86</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-0.20% / -2.80%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (3g/0/%95)
+E - TP2/10G - %81 / 147 işlem - ADAY (3g/0/%75)</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 67 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>263.94500732</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+ALT -  - 23/1 , SHORT - 144 - 23/4 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>UMID(1) %87</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-0.58% / -2.80%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (3g/-1/%95)
+E - TP2/10G - %81 / 147 işlem - ADAY (3g/-1/%75)</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 67 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>128.83999634</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 11 - 18/7 , ALT -  - 11/1 , SHORT - 10 - 10/0</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>N24(1) %100
+URSI(1) %88
+UDEP(1) %88</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-7.96% / -3.65%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %86 / 29 işlem - ONAY (5g/-8/%92)</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: MOMENTUM_3_6_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>138.59939575</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+SHORT - 15 - 14/3 , LONG - 43 - 23/9 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D1_DC05-TP2/10G, D2_DC05-TP2/10G, D3_NU03-TP2/10G, D3_NU03-TP5/20G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (1g/+1/%100)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (1g/+1/%100)
+D3_NU03 - TP2/10G - %81 / 72 işlem - ADAY (1g/+1/%100)
+D3_NU03 - TP5/20G - %79 / 62 işlem - ADAY (1g/+1/%100)
+E - TP2/10G - %81 / 147 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga, D3_NU03: V3 | Kalici PFY icinde SIS bir rapor sonra yeniden LONG, E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 121 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>71.85990142999999</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+LONG - 11 - 12/0 , LONG - 11 - 7/3 , -</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, D1_DU01-TP2/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (3g/-2/%75)
+D1_DU01 - TP2/10G - %81 / 31 işlem - ADAY (3g/-2/%56)
+R - TP2/10G - %75 / 177 işlem - ADAY (3g/-2/%60)</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY D1_DU01: V1 | Kalici WMA trendine yeni CNDL, R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>69.20500183</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 6 - 9/3 , SHORT - 45 - 21/1 , SHORT - 1622 - 22/10</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D1_DU02-TP2/10G, D2_DU02-TP2/10G, E-TP2/10G, G-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>D1_DU02 - TP2/10G - %75 / 153 işlem - ADAY (8g/-7/%0)
+D2_DU02 - TP2/10G - %75 / 153 işlem - ADAY (8g/-7/%0)
+E - TP2/10G - %81 / 147 işlem - ADAY (7g/-6/%10)
+G - TP2/10G - %78 / 223 işlem - ADAY (7g/-6/%20)</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DU02: V1 | PFY yon degisimi ve PHL ivmesi, D2_DU02: V2 | PFY yon degisimi ve PHL ivmesi, E: PFY_GORECELI_UCUZ, G: PHL_KALITE_LAG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 85 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>921.35498047</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 8 - 2/20 , SHORT - 14 - 6/16 , SHORT - 18 - 11/13</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>N15(1) %94
+L5(9) %86
+C1(1) %100
+C3(1) %94
+LC1(1) %100
+LC2(1) %94
+LC3(1) %100</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-0.70% / -3.13%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, D3_NT02-TP5/20G, K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %87 / 30 işlem - ONAY (9g/0/%100)
+D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (14g/-3/%56)
+K - TP5/10G - %77 / 31 işlem - ADAY (9g/0/%100)</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY_S; ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife, K: PFY_S; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>496.21499634</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+ALT -  - 26/3 , ALT -  - 24/6 , SHORT - 147 - 31/3</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>D1_DC05-TP2/10G, D2_DC05-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (5g/-6/%30)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (5g/-6/%30)</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 77 hisse / 147 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>76.14499664</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 4 - 17/4 , SHORT - 27 - 18/13 , -</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>D3_NU03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>D3_NU03 - TP5/20G - %79 / 62 işlem - ADAY (6g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NU03: V3 | Kalici PFY icinde SIS bir rapor sonra yeniden LONG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 57 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>49.52999878</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 4 - 9/4 , LONG - 3 - 10/2 , LONG - 8 - 4/6</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>D1_DT02-TP5/10G, D1_DT02-TP5/20G, D2_DT02-TP5/10G, D2_DT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>D1_DT02 - TP5/10G - %83 / 18 işlem - ADAY (7g/+4/%100)
+D1_DT02 - TP5/20G - %82 / 17 işlem - ADAY (7g/+4/%100)
+D2_DT02 - TP5/10G - %83 / 18 işlem - ADAY (7g/+4/%100)
+D2_DT02 - TP5/20G - %82 / 17 işlem - ADAY (7g/+4/%100)</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DT02: V1 | PHL kisa ufkun one gecmesi ve TDA, D2_DT02: V2 | PHL kisa ufkun one gecmesi ve TDA; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 17 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>212.41999817</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+ALT -  - 14/3 , ALT -  - 12/1 , LONG - 6 - 7/3</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %81 / 147 işlem - ADAY (9g/-3/%25)</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>35.80770111</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SPGI</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX +1, TOPLAM 0, ALMA
+SHORT - 49 - 11/5 , SHORT - 13 - 9/3 , SHORT - 49 - 12/5</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %81 / 147 işlem - ADAY (1g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>404.30499268</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+SHORT - 18 - 7/3 , SHORT - 37 - 19/12 , SHORT - 30 - 7/3</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>D3_NT02-TP5/20G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (16g/-2/%43)
+R - TP2/10G - %75 / 177 işlem - ADAY (9g/-3/%25)</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife, R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 98 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>249.39480591</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 21 - 34/1 , ALT -  - 32/8 , ALT -  - 25/13</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>UINS(1) %86</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-21.71% / -5.28%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>D3_NC03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>D3_NC03 - TP5/20G - %85 / 39 işlem - ADAY (15g/-22/%29)</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NC03: V3 | SIS devaminda PHL1 yerel dipten toparlanma; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 20 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>156.25999451</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 3 - 9/1 , ALT -  - 13/0 , SHORT - 155 - 16/5</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>D1_DU02-TP2/10G, D2_DU02-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>D1_DU02 - TP2/10G - %75 / 153 işlem - ADAY (8g/-4/%10)
+D2_DU02 - TP2/10G - %75 / 153 işlem - ADAY (8g/-4/%10)</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DU02: V1 | PFY yon degisimi ve PHL ivmesi, D2_DU02: V2 | PFY yon degisimi ve PHL ivmesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 80 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>273.51000977</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX +1, TOPLAM 2, ALMA
+SHORT - 14 - 5/14 , SHORT - 14 - 5/14 , LONG - 1141 - 14/10</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>R - TP2/10G - %75 / 177 işlem - ADAY (9g/-1/%50)</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 108 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>561.10998535</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+SHORT - 7 - 9/11 , SHORT - 7 - 9/11 , LONG - 2 - 9/3</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>D3_NT02-TP2/10G, D3_NT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>D3_NT02 - TP2/10G - %83 / 35 işlem - ADAY (6g/-2/%44)
+D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (10g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>57.97499847</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 7 - 14/7 , LONG - 6 - 6/4 , LONG - 1640 - 14/16</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D3_NU05-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>D3_NU05 - TP2/10G - %81 / 16 işlem - ADAY (9g/-1/%60)</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NU05: V3 | PHL5 iki adimli ivme ve kalici TDA; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 12 hisse / 15 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>321.5249939</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+SHORT - 15 - 16/5 , LONG - 2 - 13/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>UNDX(1) %70</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-8.42% / -4.12%</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D3_NC03-TP2/10G, D3_NT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>D3_NC03 - TP2/10G - %88 / 90 işlem - ONAY (9g/-8/%0)
+D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (10g/-9/%70)</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>ONAY D3_NC03: V3 | SIS devaminda PHL1 yerel dipten toparlanma; ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 66 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>32.88499832</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX +1, TOPLAM 1, ALMA
+LONG - 6 - 13/11 , SHORT - 2 - 2/7 , SHORT - 2 - 2/7</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %86 / 29 işlem - ONAY (12g/-5/%60)</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: MOMENTUM_3_6_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>303.5</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NEM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX +1, TOPLAM -1, ALMA
+SHORT - 9 - 6/22 , SHORT - 21 - 8/2 , SHORT - 14 - 9/1</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>K-TP2/10G, K-TP5/20G, K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>K - TP2/10G - %90 / 31 işlem - ONAY (9g/-5/%25)
+K - TP5/20G - %87 / 30 işlem - ONAY (15g/-3/%0)
+K - TP5/10G - %77 / 31 işlem - ADAY (5g/-3/%67)</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY_S; ADAY K: PFY_S; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 28 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>120.91000366</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 7 - 8/8 , LONG - 8 - 4/8 , LONG - 6 - 4/6</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>D2_DT03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>D2_DT03 - TP5/20G - %76 / 34 işlem - ADAY (4g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D2_DT03: V2 | CNDL sonrasi yeni BSL ve WMA dengesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>1725.60498047</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX +1, TOPLAM 3, İZLE
+LONG - 40 - 11/18 , SHORT - 1 - 1/9 , SHORT - 1 - 1/9</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>D2_DT03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>D2_DT03 - TP5/20G - %76 / 34 işlem - ADAY (13g/0/%100)</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D2_DT03: V2 | CNDL sonrasi yeni BSL ve WMA dengesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>186.38000488</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q29"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2736,127 +4818,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q32"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Hisse</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Düne_Göre_%</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Yarın_Alım</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Puan</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Onaylı_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Aday_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Toplam_Öneren_Sistem</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>SECIM</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>SECIM (kar/DD)</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Kodları</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Detayı</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Neden</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Engel_Risk</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>Son_Fiyat</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Fiyat_Tarihi</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3226,7 +5187,7 @@
         <v>26</v>
       </c>
       <c r="U2" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V2" s="12" t="n">
         <v>100.2213974036418</v>
@@ -3413,7 +5374,7 @@
         <v>86</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V3" s="12" t="n">
         <v>100.2213974036418</v>
@@ -3600,7 +5561,7 @@
         <v>36</v>
       </c>
       <c r="U4" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V4" s="12" t="n">
         <v>100.2213974036418</v>
@@ -3787,7 +5748,7 @@
         <v>14</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V5" s="12" t="n">
         <v>100.2213974036418</v>
@@ -3974,7 +5935,7 @@
         <v>22</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V6" s="12" t="n">
         <v>100.2213974036418</v>
@@ -4161,7 +6122,7 @@
         <v>15</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V7" s="12" t="n">
         <v>100.2213974036418</v>
@@ -4348,7 +6309,7 @@
         <v>16</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V8" s="12" t="n">
         <v>100.2213974036418</v>
@@ -4535,7 +6496,7 @@
         <v>147</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V9" s="12" t="n">
         <v>100.2213974036418</v>
@@ -4722,7 +6683,7 @@
         <v>23</v>
       </c>
       <c r="U10" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V10" s="12" t="n">
         <v>100.2213974036418</v>
@@ -4909,7 +6870,7 @@
         <v>35</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V11" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5096,7 +7057,7 @@
         <v>17</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V12" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5283,7 +7244,7 @@
         <v>16</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V13" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5470,7 +7431,7 @@
         <v>16</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V14" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5657,7 +7618,7 @@
         <v>29</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V15" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5844,7 +7805,7 @@
         <v>53</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V16" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6031,7 +7992,7 @@
         <v>127</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V17" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6218,7 +8179,7 @@
         <v>24</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6405,7 +8366,7 @@
         <v>20</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V19" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6592,7 +8553,7 @@
         <v>147</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6779,7 +8740,7 @@
         <v>23</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V21" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6966,7 +8927,7 @@
         <v>35</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V22" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7153,7 +9114,7 @@
         <v>17</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V23" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7340,7 +9301,7 @@
         <v>16</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V24" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7527,7 +9488,7 @@
         <v>34</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V25" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7714,7 +9675,7 @@
         <v>33</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V26" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7901,7 +9862,7 @@
         <v>53</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V27" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8088,7 +10049,7 @@
         <v>15</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V28" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8275,7 +10236,7 @@
         <v>14</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V29" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8462,7 +10423,7 @@
         <v>41</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V30" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8649,7 +10610,7 @@
         <v>127</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V31" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8836,7 +10797,7 @@
         <v>77</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9023,7 +10984,7 @@
         <v>39</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V33" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9210,7 +11171,7 @@
         <v>37</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V34" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9397,7 +11358,7 @@
         <v>20</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V35" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9584,7 +11545,7 @@
         <v>20</v>
       </c>
       <c r="U36" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V36" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9771,7 +11732,7 @@
         <v>30</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V37" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9958,7 +11919,7 @@
         <v>21</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V38" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10145,7 +12106,7 @@
         <v>26</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V39" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10332,7 +12293,7 @@
         <v>14</v>
       </c>
       <c r="U40" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V40" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10519,7 +12480,7 @@
         <v>14</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V41" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10706,7 +12667,7 @@
         <v>16</v>
       </c>
       <c r="U42" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V42" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10893,7 +12854,7 @@
         <v>16</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V43" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11080,7 +13041,7 @@
         <v>27</v>
       </c>
       <c r="U44" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V44" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11267,7 +13228,7 @@
         <v>27</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V45" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11454,7 +13415,7 @@
         <v>26</v>
       </c>
       <c r="U46" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V46" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11641,7 +13602,7 @@
         <v>32</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V47" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11828,7 +13789,7 @@
         <v>66</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V48" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12015,7 +13976,7 @@
         <v>57</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V49" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12202,7 +14163,7 @@
         <v>15</v>
       </c>
       <c r="U50" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V50" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12389,7 +14350,7 @@
         <v>91</v>
       </c>
       <c r="U51" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V51" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12576,7 +14537,7 @@
         <v>42</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V52" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12763,7 +14724,7 @@
         <v>125</v>
       </c>
       <c r="U53" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V53" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12950,7 +14911,7 @@
         <v>26</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V54" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13137,7 +15098,7 @@
         <v>38</v>
       </c>
       <c r="U55" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V55" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13324,7 +15285,7 @@
         <v>35</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V56" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13511,7 +15472,7 @@
         <v>28</v>
       </c>
       <c r="U57" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V57" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13698,7 +15659,7 @@
         <v>28</v>
       </c>
       <c r="U58" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V58" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13885,7 +15846,7 @@
         <v>27</v>
       </c>
       <c r="U59" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V59" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14072,7 +16033,7 @@
         <v>24</v>
       </c>
       <c r="U60" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V60" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14259,7 +16220,7 @@
         <v>47</v>
       </c>
       <c r="U61" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V61" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14446,7 +16407,7 @@
         <v>47</v>
       </c>
       <c r="U62" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V62" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14633,7 +16594,7 @@
         <v>27</v>
       </c>
       <c r="U63" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V63" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14820,7 +16781,7 @@
         <v>26</v>
       </c>
       <c r="U64" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V64" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15007,7 +16968,7 @@
         <v>32</v>
       </c>
       <c r="U65" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V65" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15194,7 +17155,7 @@
         <v>15</v>
       </c>
       <c r="U66" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V66" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15381,7 +17342,7 @@
         <v>31</v>
       </c>
       <c r="U67" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V67" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15568,7 +17529,7 @@
         <v>26</v>
       </c>
       <c r="U68" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V68" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15755,7 +17716,7 @@
         <v>20</v>
       </c>
       <c r="U69" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V69" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15942,7 +17903,7 @@
         <v>26</v>
       </c>
       <c r="U70" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V70" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16129,7 +18090,7 @@
         <v>71</v>
       </c>
       <c r="U71" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V71" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16316,7 +18277,7 @@
         <v>108</v>
       </c>
       <c r="U72" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V72" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16503,7 +18464,7 @@
         <v>20</v>
       </c>
       <c r="U73" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V73" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16690,7 +18651,7 @@
         <v>38</v>
       </c>
       <c r="U74" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V74" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16877,7 +18838,7 @@
         <v>43</v>
       </c>
       <c r="U75" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V75" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17064,7 +19025,7 @@
         <v>25</v>
       </c>
       <c r="U76" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V76" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17251,7 +19212,7 @@
         <v>13</v>
       </c>
       <c r="U77" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V77" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17438,7 +19399,7 @@
         <v>25</v>
       </c>
       <c r="U78" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V78" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17625,7 +19586,7 @@
         <v>17</v>
       </c>
       <c r="U79" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V79" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17812,7 +19773,7 @@
         <v>23</v>
       </c>
       <c r="U80" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V80" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17999,7 +19960,7 @@
         <v>49</v>
       </c>
       <c r="U81" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V81" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18186,7 +20147,7 @@
         <v>14</v>
       </c>
       <c r="U82" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V82" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18373,7 +20334,7 @@
         <v>19</v>
       </c>
       <c r="U83" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V83" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18560,7 +20521,7 @@
         <v>37</v>
       </c>
       <c r="U84" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V84" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18747,7 +20708,7 @@
         <v>44</v>
       </c>
       <c r="U85" s="13" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="V85" s="12" t="n">
         <v>100.2213974036418</v>

--- a/TSBT_usa.xlsx
+++ b/TSBT_usa.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$Q$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dün'!$A$1:$Q$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dün'!$A$1:$Q$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$AS$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,6 +472,1933 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>SECIM</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>SECIM (kar/DD)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="132" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+SHORT - 12 - 20/6 , ALT -  - 11/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>X13(1) %100
+L2(2) %100
+L5(13) %86
+MULTI(1) %90
+C1(1) %100
+C2(1) %94
+LC1(1) %100
+LC2(1) %94
+LC3(1) %100
+URSI(1) %88
+UMID(1) %87</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-8.90% / -3.65%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>D3_NT03-TP2/10G, P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>D3_NT03 - TP2/10G - %97 / 31 işlem - ONAY (0g/0/%100)
+P - TP5/20G - %86 / 29 işlem - ONAY (6g/-9/%83)</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>ONAY D3_NT03: V3 | BIS ayrismasi biterken TDA gucleniyor, P: MOMENTUM_3_6_COKLU_TEYIT; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>137.18499756</v>
+      </c>
+      <c r="Q2" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+SHORT - 66 - 24/8 , SHORT - 46 - 16/5 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>UVP(1) %100
+UBND(1) %88</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-3.52% / -3.08%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, A-TP2/10G, D1_DC05-TP2/10G, D2_DC05-TP2/10G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (6g/-4/%60)
+A - TP2/10G - %84 / 32 işlem - ADAY (6g/-4/%50)
+D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (6g/-4/%50)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (6g/-4/%50)
+E - TP2/10G - %81 / 147 işlem - ADAY (6g/-4/%35)</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY A: CNDL_GECIKMIS, D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga, E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 114 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>196.3500061</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX -1, TOPLAM -2, ALMA
+ALT -  - 23/11 , ALT -  - 11/0 , ALT -  - 20/6</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>L5(1) %88</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-2.58% / -2.74%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP2/10G, Q-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (6g/-3/%75)
+E - TP2/10G - %81 / 147 işlem - ADAY (6g/-3/%40)
+Q - TP2/10G - %77 / 92 işlem - ADAY (6g/-3/%65)</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ, Q: CNDL_GECIKMIS_GORECELI_GERI_KALAN; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 68 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>189.18499756</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+UST -  - 1/19 , UST -  - 1/19 , UST -  - 5/14</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>N15(1) %94
+N16(1) %100
+L5(10) %86
+C3(1) %94
+UFLO(1) %83</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>+0.02% / -2.80%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (4g/0/%100)
+E - TP2/10G - %81 / 147 işlem - ADAY (4g/0/%100)</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 67 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>264.53500366</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, NDX -1, TOPLAM -2, ALMA
+ALT -  - 24/1 , SHORT - 145 - 23/4 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>C4(1) %89</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.78% / -2.80%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (4g/-1/%75)
+E - TP2/10G - %81 / 147 işlem - ADAY (4g/-1/%55)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 67 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>128.58000183</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 16 - 15/2 , LONG - 44 - 24/8 , ALT -  - 13/3</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>D1_DC05-TP2/10G, D2_DC05-TP2/10G, D3_NU03-TP2/10G, D3_NU03-TP5/20G, E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (2g/0/%85)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (2g/0/%85)
+D3_NU03 - TP2/10G - %81 / 72 işlem - ADAY (2g/0/%65)
+D3_NU03 - TP5/20G - %79 / 62 işlem - ADAY (2g/0/%95)
+E - TP2/10G - %81 / 147 işlem - ADAY (2g/0/%90)</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga, D3_NU03: V3 | Kalici PFY icinde SIS bir rapor sonra yeniden LONG, E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 121 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>71.09500122</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 3 - 12/1 , ALT -  - 15/4 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>L5(1) %100</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-2.43% / -3.45%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>V-TP5/20G, D1_DC05-TP2/10G, D2_DC05-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>V - TP5/20G - %89 / 27 işlem - ONAY (16g/-5/%67)
+D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (4g/-2/%75)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (4g/-2/%75)</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY V: MIRAS_WMA_TEYITLI; ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 140 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>197.93499756</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 7 - 14/3 , LONG - 8 - 20/5 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>D-TP5/20G, D2_DU03-TP5/20G, D3_NT03-TP5/20G, E-TP2/10G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>D - TP5/20G - %76 / 17 işlem - ADAY (12g/-3/%83)
+D2_DU03 - TP5/20G - %80 / 44 işlem - ADAY (19g/-4/%13)
+D3_NT03 - TP5/20G - %87 / 15 işlem - ADAY (12g/-3/%50)
+E - TP2/10G - %81 / 147 işlem - ADAY (1g/+1/%100)
+Y - TP5/20G - %80 / 49 işlem - ADAY (19g/-4/%13)</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D: TDA_GERI_CEKILME, D2_DU03: V2 | Yeni SIS icin TDA teyidi ve ATL risk elemesi, D3_NT03: V3 | BIS ayrismasi biterken TDA gucleniyor, E: PFY_GORECELI_UCUZ, Y: COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>353.10501099</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+UST -  - 2/23 , SHORT - 15 - 3/19 , SHORT - 19 - 7/16</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, D3_NT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %87 / 30 işlem - ONAY (10g/+4/%100)
+D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (15g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY_S; ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 24 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>516.28997803</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 12 - 11/1 , LONG - 12 - 6/4 , -</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>N24(1) %100</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-1.70% / -3.16%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, D1_DU01-TP2/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %85 / 123 işlem - ONAY (4g/-2/%75)
+D1_DU01 - TP2/10G - %81 / 31 işlem - ADAY (4g/-2/%55)
+R - TP2/10G - %75 / 177 işlem - ADAY (4g/-2/%70)</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY D1_DU01: V1 | Kalici WMA trendine yeni CNDL, R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>69.63500214</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 7 - 7/5 , SHORT - 46 - 19/3 , SHORT - 1623 - 19/12</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D1_DU02-TP2/10G, D2_DU02-TP2/10G, E-TP2/10G, G-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>D1_DU02 - TP2/10G - %75 / 153 işlem - ADAY (9g/-5/%5)
+D2_DU02 - TP2/10G - %75 / 153 işlem - ADAY (9g/-5/%5)
+E - TP2/10G - %81 / 147 işlem - ADAY (8g/-4/%10)
+G - TP2/10G - %78 / 223 işlem - ADAY (8g/-4/%30)</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DU02: V1 | PFY yon degisimi ve PHL ivmesi, D2_DU02: V2 | PFY yon degisimi ve PHL ivmesi, E: PFY_GORECELI_UCUZ, G: PHL_KALITE_LAG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 85 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>935.72998047</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+ALT -  - 26/3 , ALT -  - 24/6 , SHORT - 148 - 31/3</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D1_DC05-TP2/10G, D2_DC05-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (6g/-6/%15)
+D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (6g/-6/%15)</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 77 hisse / 147 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>76.01999664</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+LONG - 5 - 18/3 , SHORT - 28 - 19/12 , -</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>D3_NU03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>D3_NU03 - TP5/20G - %79 / 62 işlem - ADAY (7g/0/%58)</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NU03: V3 | Kalici PFY icinde SIS bir rapor sonra yeniden LONG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 57 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>48.79000092</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SPGI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX -1, TOPLAM 0, ALMA
+SHORT - 50 - 11/5 , SHORT - 14 - 9/3 , SHORT - 50 - 12/5</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>E-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %81 / 147 işlem - ADAY (2g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>403.59500122</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+LONG - 4 - 9/1 , LONG - 3 - 12/0 , SHORT - 156 - 15/6</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>D1_DU02-TP2/10G, D2_DU02-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>D1_DU02 - TP2/10G - %75 / 153 işlem - ADAY (9g/-4/%10)
+D2_DU02 - TP2/10G - %75 / 153 işlem - ADAY (9g/-4/%10)</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D1_DU02: V1 | PFY yon degisimi ve PHL ivmesi, D2_DU02: V2 | PFY yon degisimi ve PHL ivmesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 80 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>273.70999146</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, NDX -1, TOPLAM -2, ALMA
+SHORT - 22 - 27/6 , ALT -  - 25/2 , ALT -  - 19/7</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>D3_NC03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>D3_NC03 - TP5/20G - %85 / 39 işlem - ADAY (16g/-18/%29)</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NC03: V3 | SIS devaminda PHL1 yerel dipten toparlanma; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 20 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>163.92999268</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 19 - 7/3 , SHORT - 38 - 18/13 , SHORT - 31 - 7/3</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>D3_NT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (17g/-2/%43)</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 19 hisse / 21 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>249.60499573</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 16 - 16/5 , ALT -  - 13/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>D3_NT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (11g/-9/%63)</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 19 hisse / 21 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>32.73500061</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 8 - 8/8 , SHORT - 8 - 8/8 , SHORT - 161 - 13/8</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>R - TP2/10G - %75 / 177 işlem - ADAY (1g/0/%90)</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 108 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>47.125</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
+SHORT - 8 - 11/9 , SHORT - 8 - 11/9 , LONG - 3 - 11/2</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>D3_NT02-TP2/10G, D3_NT02-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>D3_NT02 - TP2/10G - %83 / 35 işlem - ADAY (7g/-4/%29)
+D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (11g/-7/%63)</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>56.80500031</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, NDX -1, TOPLAM 0, ALMA
+LONG - 1 - 10/2 , SHORT - 87 - 12/4 , LONG - 5 - 9/3</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>D3_NU01-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>D3_NU01 - TP2/10G - %77 / 31 işlem - ADAY (9g/0/%100)</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D3_NU01: V3 | Uzun WMA LONG icinde kisa WMA yeniden giris; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 20 hisse / 27 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>922.53997803</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, NDX -1, TOPLAM 0, ALMA
+ALT -  - 23/1 , ALT -  - 19/5 , ALT -  - 18/7</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>J-TP2/10G</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>J - TP2/10G - %75 / 36 işlem - ADAY (1g/-1/%73)</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY J: SABIT_DENETIM; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>21.91500092</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 7 - 9/14 , UST -  - 1/10 , UST -  - 1/10</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %86 / 29 işlem - ONAY (13g/-2/%60)</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: MOMENTUM_3_6_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>315.52999878</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NEM</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+SHORT - 10 - 6/22 , SHORT - 22 - 7/3 , SHORT - 15 - 8/2</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>L2(1) %100</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-2.67% / -2.27%</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %87 / 30 işlem - ONAY (16g/-3/%0)
+K - TP5/10G - %77 / 31 işlem - ADAY (6g/-2/%70)</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY_S; ADAY K: PFY_S; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 28 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>121.47000122</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
+LONG - 41 - 11/18 , SHORT - 2 - 0/9 , SHORT - 2 - 1/9</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D2_DT03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>D2_DT03 - TP5/20G - %76 / 34 işlem - ADAY (14g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D2_DT03: V2 | CNDL sonrasi yeni BSL ve WMA dengesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>188.00999451</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
+LONG - 8 - 7/9 , LONG - 9 - 3/9 , LONG - 7 - 3/7</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>D2_DT03-TP5/20G</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>D2_DT03 - TP5/20G - %76 / 34 işlem - ADAY (5g/+4/%100)</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY D2_DT03: V2 | CNDL sonrasi yeni BSL ve WMA dengesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>1744.48999023</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q27"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2544,2280 +4471,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q29"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Hisse</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Düne_Göre_%</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Yarın_Alım</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Puan</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Onaylı_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Aday_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Toplam_Öneren_Sistem</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>SECIM</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>SECIM (kar/DD)</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Kodları</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Detayı</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Neden</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Engel_Risk</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>Son_Fiyat</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Fiyat_Tarihi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 64 - 23/9 , SHORT - 44 - 15/6 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>L3(1) %88
-L5(9) %88
-MULTI(1) %90</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-2.31% / -3.08%</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, A-TP2/10G, D1_DC05-TP2/10G, D2_DC05-TP2/10G, E-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %85 / 123 işlem - ONAY (4g/-2/%70)
-A - TP2/10G - %84 / 32 işlem - ADAY (4g/-2/%55)
-D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (4g/-2/%60)
-D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (4g/-2/%60)
-E - TP2/10G - %81 / 147 işlem - ADAY (4g/-2/%55)</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY A: CNDL_GECIKMIS, D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga, E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 114 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P2" s="8" t="n">
-        <v>198.81500244</v>
-      </c>
-      <c r="Q2" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-LONG - 1 - 11/2 , LONG - 3 - 10/3 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="7" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>V-TP5/20G, D1_DC05-TP2/10G, D2_DC05-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>V - TP5/20G - %89 / 27 işlem - ONAY (14g/-4/%88)
-D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (2g/0/%100)
-D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (2g/0/%100)</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY V: MIRAS_WMA_TEYITLI; ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 140 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="n">
-        <v>201.41000366</v>
-      </c>
-      <c r="Q3" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 21/9 , LONG - 2 - 10/1 , ALT -  - 18/5</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="7" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, E-TP2/10G, Q-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %85 / 123 işlem - ONAY (4g/-1/%75)
-E - TP2/10G - %81 / 147 işlem - ADAY (4g/-1/%55)
-Q - TP2/10G - %77 / 92 işlem - ADAY (4g/-1/%80)</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ, Q: CNDL_GECIKMIS_GORECELI_GERI_KALAN; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 68 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="n">
-        <v>192.89590454</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-ALT -  - 13/0 , SHORT - 85 - 15/2 , LONG - 3 - 12/1</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>L5(1) %88
-C4(1) %89</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.25% / -3.15%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, D3_NU01-TP2/10G, G-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %85 / 123 işlem - ONAY (4g/+1/%100)
-D3_NU01 - TP2/10G - %77 / 31 işlem - ADAY (7g/-2/%56)
-G - TP2/10G - %78 / 223 işlem - ADAY (8g/0/%45)</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY D3_NU01: V3 | Uzun WMA LONG icinde kisa WMA yeniden giris, G: PHL_KALITE_LAG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 89 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v>900.6799926800001</v>
-      </c>
-      <c r="Q5" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 14 - 15/2 , LONG - 42 - 24/9 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>UVP(1) %100</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>+0.00% / -3.41%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>D1_DC05-TP2/10G, D2_DC05-TP2/10G, D3_NU03-TP2/10G, D3_NU03-TP5/20G, E-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (0g/0/%100)
-D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (0g/0/%100)
-D3_NU03 - TP2/10G - %81 / 72 işlem - ADAY (0g/0/%100)
-D3_NU03 - TP5/20G - %79 / 62 işlem - ADAY (0g/0/%100)
-E - TP2/10G - %81 / 147 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga, D3_NU03: V3 | Kalici PFY icinde SIS bir rapor sonra yeniden LONG, E: PFY_GORECELI_UCUZ; Bugün 5 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 65 hisse / 121 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>71.66000366</v>
-      </c>
-      <c r="Q6" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ABBV</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-UST -  - 1/19 , UST -  - 1/19 , UST -  - 6/15</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N15(1) %94
-N16(1) %100
-L5(10) %86
-C3(1) %94
-UFLO(1) %83</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-0.15% / -2.80%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, E-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %85 / 123 işlem - ONAY (2g/0/%85)
-E - TP2/10G - %81 / 147 işlem - ADAY (2g/0/%90)</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 67 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>264.09500122</v>
-      </c>
-      <c r="Q7" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX -1, TOPLAM -2, ALMA
-ALT -  - 23/1 , SHORT - 143 - 22/4 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, E-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %85 / 123 işlem - ONAY (2g/0/%100)
-E - TP2/10G - %81 / 147 işlem - ADAY (2g/0/%100)</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 67 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>129.6401062</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, NDX -1, TOPLAM 2, ALMA
-LONG - 10 - 12/0 , LONG - 10 - 7/3 , -</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N24(1) %100
-L3(4) %100
-L5(5) %86
-LC3(1) %100</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-1.75% / -3.16%</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, D1_DU01-TP2/10G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %85 / 123 işlem - ONAY (2g/-2/%80)
-D1_DU01 - TP2/10G - %81 / 31 işlem - ADAY (2g/-2/%63)
-R - TP2/10G - %75 / 177 işlem - ADAY (2g/-2/%85)</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: ENDEKS_YUKSELIRKEN_GERI_KALAN; ADAY D1_DU01: V1 | Kalici WMA trendine yeni CNDL, R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>69.59999847</v>
-      </c>
-      <c r="Q9" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 5 - 14/3 , LONG - 6 - 20/5 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="7" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>D-TP5/20G, D2_DU03-TP5/20G, D3_NT03-TP5/20G, D3_NU02-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>D - TP5/20G - %76 / 17 işlem - ADAY (10g/-3/%88)
-D2_DU03 - TP5/20G - %80 / 44 işlem - ADAY (17g/-4/%33)
-D3_NT03 - TP5/20G - %87 / 15 işlem - ADAY (10g/-3/%67)
-D3_NU02 - TP5/20G - %81 / 37 işlem - ADAY (18g/-5/%33)
-Y - TP5/20G - %80 / 49 işlem - ADAY (17g/-4/%22)</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D: TDA_GERI_CEKILME, D2_DU03: V2 | Yeni SIS icin TDA teyidi ve ATL risk elemesi, D3_NT03: V3 | BIS ayrismasi biterken TDA gucleniyor, D3_NU02: V3 | TDA iki raporda guclenirken yeni CNDL LONG, Y: COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>354.66500854</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-LONG - 5 - 8/4 , SHORT - 44 - 19/3 , SHORT - 1621 - 20/11</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>D1_DU02-TP2/10G, D2_DU02-TP2/10G, E-TP2/10G, G-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>D1_DU02 - TP2/10G - %75 / 153 işlem - ADAY (7g/-5/%20)
-D2_DU02 - TP2/10G - %75 / 153 işlem - ADAY (7g/-5/%20)
-E - TP2/10G - %81 / 147 işlem - ADAY (6g/-4/%30)
-G - TP2/10G - %78 / 223 işlem - ADAY (6g/-4/%30)</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D1_DU02: V1 | PFY yon degisimi ve PHL ivmesi, D2_DU02: V2 | PFY yon degisimi ve PHL ivmesi, E: PFY_GORECELI_UCUZ, G: PHL_KALITE_LAG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 85 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>937.3150024399999</v>
-      </c>
-      <c r="Q11" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-LONG - 6 - 14/6 , LONG - 5 - 6/4 , LONG - 1639 - 13/16</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>D3_NT03-TP2/10G, D3_NU05-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>D3_NT03 - TP2/10G - %97 / 31 işlem - ONAY (9g/-1/%80)
-D3_NU05 - TP2/10G - %81 / 16 işlem - ADAY (8g/-1/%67)</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>ONAY D3_NT03: V3 | BIS ayrismasi biterken TDA gucleniyor; ADAY D3_NU05: V3 | PHL5 iki adimli ivme ve kalici TDA; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>321.3500061</v>
-      </c>
-      <c r="Q12" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX -1, TOPLAM 0, ALMA
-SHORT - 7 - 1/20 , SHORT - 13 - 5/17 , SHORT - 17 - 10/14</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>K-TP5/20G, D3_NT02-TP5/20G, K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %87 / 30 işlem - ONAY (8g/+1/%100)
-D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (13g/-2/%63)
-K - TP5/10G - %77 / 31 işlem - ADAY (8g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY_S; ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife, K: PFY_S; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>499.27999878</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-ALT -  - 24/1 , ALT -  - 22/4 , SHORT - 146 - 29/5</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>D1_DC05-TP2/10G, D2_DC05-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>D1_DC05 - TP2/10G - %82 / 233 işlem - ADAY (4g/-4/%35)
-D2_DC05 - TP2/10G - %82 / 233 işlem - ADAY (4g/-4/%35)</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D1_DC05: V1 | Dortlu teyitte azinliktan cogunluga, D2_DC05: V2 | Dortlu teyitte azinliktan cogunluga; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 77 hisse / 147 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>77.74500275</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 3 - 18/3 , SHORT - 26 - 20/12 , -</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>D3_NU03-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>D3_NU03 - TP5/20G - %79 / 62 işlem - ADAY (5g/0/%100)</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D3_NU03: V3 | Kalici PFY icinde SIS bir rapor sonra yeniden LONG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 57 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="n">
-        <v>49.06000137</v>
-      </c>
-      <c r="Q15" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, NDX -1, TOPLAM -2, ALMA
-LONG - 2 - 10/3 , LONG - 2 - 10/2 , LONG - 7 - 4/6</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>D1_DT02-TP5/10G, D1_DT02-TP5/20G, D2_DT02-TP5/10G, D2_DT02-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>D1_DT02 - TP5/10G - %83 / 18 işlem - ADAY (6g/+4/%100)
-D1_DT02 - TP5/20G - %82 / 17 işlem - ADAY (6g/+4/%100)
-D2_DT02 - TP5/10G - %83 / 18 işlem - ADAY (6g/+4/%100)
-D2_DT02 - TP5/20G - %82 / 17 işlem - ADAY (6g/+4/%100)</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D1_DT02: V1 | PHL kisa ufkun one gecmesi ve TDA, D2_DT02: V2 | PHL kisa ufkun one gecmesi ve TDA; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 17 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>211.97999573</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, NDX -1, TOPLAM 0, ALMA
-ALT -  - 14/3 , ALT -  - 12/2 , LONG - 5 - 8/3</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>E-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %81 / 147 işlem - ADAY (8g/-3/%25)</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY_GORECELI_UCUZ; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>35.83499908</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 20 - 33/1 , ALT -  - 33/8 , ALT -  - 25/13</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>URSI(1) %88</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-21.54% / -5.28%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>D3_NC03-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>D3_NC03 - TP5/20G - %85 / 39 işlem - ADAY (14g/-22/%29)</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D3_NC03: V3 | SIS devaminda PHL1 yerel dipten toparlanma; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 20 hisse / 37 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>156.60510254</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 2 - 8/2 , LONG - 1 - 12/1 , SHORT - 154 - 15/6</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>D1_DU02-TP2/10G, D2_DU02-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>D1_DU02 - TP2/10G - %75 / 153 işlem - ADAY (7g/-3/%30)
-D2_DU02 - TP2/10G - %75 / 153 işlem - ADAY (7g/-3/%30)</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D1_DU02: V1 | PFY yon degisimi ve PHL ivmesi, D2_DU02: V2 | PFY yon degisimi ve PHL ivmesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 80 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>276.66500854</v>
-      </c>
-      <c r="Q19" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 44 - 17/1 , SHORT - 44 - 22/10 , SHORT - 51 - 24/8</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>G-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>G - TP2/10G - %78 / 223 işlem - ADAY (9g/-5/%0)</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY G: PHL_KALITE_LAG; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 125 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>370.66000366</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 17 - 7/3 , SHORT - 36 - 19/12 , SHORT - 29 - 8/3</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>D3_NT02-TP5/20G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (15g/-3/%43)
-R - TP2/10G - %75 / 177 işlem - ADAY (8g/-3/%35)</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife, R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 98 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>248.08000183</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 13 - 5/14 , SHORT - 13 - 5/14 , SHORT - 17 - 7/3</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>R - TP2/10G - %75 / 177 işlem - ADAY (8g/-2/%45)</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 108 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>559.77502441</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>OXY</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, NDX -1, TOPLAM -3, ALMA
-SHORT - 6 - 9/10 , SHORT - 6 - 9/10 , LONG - 1 - 10/2</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="7" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>D3_NT02-TP2/10G, D3_NT02-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>D3_NT02 - TP2/10G - %83 / 35 işlem - ADAY (5g/-3/%50)
-D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (9g/-6/%63)</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 26 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>57.52500153</v>
-      </c>
-      <c r="Q23" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 14 - 15/6 , LONG - 1 - 12/1 , LONG - 1 - 10/0</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>UBND(1) %88</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>-7.91% / -3.68%</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>D3_NC03-TP2/10G, D3_NT02-TP2/10G, D3_NT02-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>D3_NC03 - TP2/10G - %88 / 90 işlem - ONAY (8g/-8/%9)
-D3_NT02 - TP2/10G - %83 / 35 işlem - ADAY (9g/-8/%33)
-D3_NT02 - TP5/20G - %83 / 23 işlem - ADAY (9g/-8/%63)</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>ONAY D3_NC03: V3 | SIS devaminda PHL1 yerel dipten toparlanma; ADAY D3_NT02: V3 | ATL devaminda PHL3 negatiften pozitife; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 57 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>33.11000061</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ANET</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, NDX -1, TOPLAM -2, ALMA
-LONG - 23 - 3/7 , LONG - 23 - 3/7 , UST -  - 2/11</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %86 / 29 işlem - ONAY (19g/0/%100)</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: MOMENTUM_3_6_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>202.55000305</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 5 - 12/12 , SHORT - 1 - 2/8 , SHORT - 1 - 2/8</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %86 / 29 işlem - ONAY (11g/-5/%50)</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: MOMENTUM_3_6_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>305.51998901</v>
-      </c>
-      <c r="Q26" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ORCL</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-LONG - 37 - 22/10 , LONG - 6 - 7/4 , SHORT - 9 - 5/5</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>UMID(1) %87</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>-2.67% / -3.65%</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %86 / 29 işlem - ONAY (4g/-3/%90)</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: MOMENTUM_3_6_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 26 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>146.56500244</v>
-      </c>
-      <c r="Q27" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="28" ht="84" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEM</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-SHORT - 8 - 4/23 , UST -  - 1/19 , SHORT - 13 - 7/3</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>X13(1) %100
-C1(1) %100
-C2(1) %94
-LC1(1) %100
-LC2(1) %94
-UTRD(1) %88
-UDEP(1) %88</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-1.75% / -1.95%</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>K-TP2/10G, K-TP5/20G, K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>K - TP2/10G - %90 / 31 işlem - ONAY (8g/-3/%25)
-K - TP5/20G - %87 / 30 işlem - ONAY (14g/-1/%0)
-K - TP5/10G - %77 / 31 işlem - ADAY (4g/-1/%73)</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY_S; ADAY K: PFY_S; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 23 hisse / 28 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>123.30500031</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 39 - 10/19 , SHORT - 1 - 0/9 , SHORT - 1 - 0/9</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>D2_DT03-TP5/20G, X-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>D2_DT03 - TP5/20G - %76 / 34 işlem - ADAY (12g/0/%100)
-X - TP5/20G - %86 / 22 işlem - ADAY (19g/+1/%100)
-Y - TP5/20G - %80 / 49 işlem - ADAY (19g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D2_DT03: V2 | CNDL sonrasi yeni BSL ve WMA dengesi, X: SISTEM_KOMBINASYON, Y: COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="n">
-        <v>186.30000305</v>
-      </c>
-      <c r="Q29" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AMAT</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-LONG - 3 - 17/4 , SHORT - 1 - 0/10 , LONG - 4 - 1/9</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>X-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>X - TP5/20G - %86 / 22 işlem - ADAY (19g/-2/%100)</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>ADAY X: SISTEM_KOMBINASYON; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 19 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>470.66500854</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, NDX -1, TOPLAM -1, ALMA
-SHORT - 13 - 4/15 , SHORT - 13 - 4/15 , UST -  - 1/11</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>R - TP2/10G - %75 / 177 işlem - ADAY (3g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5_ERKEN_DONUS_COKLU_TEYIT; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 108 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>28.05990028</v>
-      </c>
-      <c r="Q31" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ASML</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, NDX -1, TOPLAM 1, ALMA
-LONG - 6 - 8/8 , LONG - 7 - 3/8 , LONG - 5 - 4/6</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>D2_DT03-TP5/20G</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>D2_DT03 - TP5/20G - %76 / 34 işlem - ADAY (3g/+3/%100)</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY D2_DT03: V2 | CNDL sonrasi yeni BSL ve WMA dengesi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 33 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>1725.32995605</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>46288</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5187,7 +4840,7 @@
         <v>26</v>
       </c>
       <c r="U2" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V2" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5374,7 +5027,7 @@
         <v>86</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V3" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5561,7 +5214,7 @@
         <v>36</v>
       </c>
       <c r="U4" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V4" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5748,7 +5401,7 @@
         <v>14</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V5" s="12" t="n">
         <v>100.2213974036418</v>
@@ -5935,7 +5588,7 @@
         <v>22</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V6" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6122,7 +5775,7 @@
         <v>15</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V7" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6309,7 +5962,7 @@
         <v>16</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V8" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6496,7 +6149,7 @@
         <v>147</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V9" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6683,7 +6336,7 @@
         <v>23</v>
       </c>
       <c r="U10" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V10" s="12" t="n">
         <v>100.2213974036418</v>
@@ -6870,7 +6523,7 @@
         <v>35</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V11" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7057,7 +6710,7 @@
         <v>17</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V12" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7244,7 +6897,7 @@
         <v>16</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V13" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7431,7 +7084,7 @@
         <v>16</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V14" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7618,7 +7271,7 @@
         <v>29</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V15" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7805,7 +7458,7 @@
         <v>53</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V16" s="12" t="n">
         <v>100.2213974036418</v>
@@ -7992,7 +7645,7 @@
         <v>127</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V17" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8179,7 +7832,7 @@
         <v>24</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8366,7 +8019,7 @@
         <v>20</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V19" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8553,7 +8206,7 @@
         <v>147</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8740,7 +8393,7 @@
         <v>23</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V21" s="12" t="n">
         <v>100.2213974036418</v>
@@ -8927,7 +8580,7 @@
         <v>35</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V22" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9114,7 +8767,7 @@
         <v>17</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V23" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9301,7 +8954,7 @@
         <v>16</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V24" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9488,7 +9141,7 @@
         <v>34</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V25" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9675,7 +9328,7 @@
         <v>33</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V26" s="12" t="n">
         <v>100.2213974036418</v>
@@ -9862,7 +9515,7 @@
         <v>53</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V27" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10049,7 +9702,7 @@
         <v>15</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V28" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10236,7 +9889,7 @@
         <v>14</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V29" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10423,7 +10076,7 @@
         <v>41</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V30" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10610,7 +10263,7 @@
         <v>127</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V31" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10797,7 +10450,7 @@
         <v>77</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>100.2213974036418</v>
@@ -10984,7 +10637,7 @@
         <v>39</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V33" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11171,7 +10824,7 @@
         <v>37</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V34" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11358,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V35" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11545,7 +11198,7 @@
         <v>20</v>
       </c>
       <c r="U36" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V36" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11732,7 +11385,7 @@
         <v>30</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V37" s="12" t="n">
         <v>100.2213974036418</v>
@@ -11919,7 +11572,7 @@
         <v>21</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V38" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12106,7 +11759,7 @@
         <v>26</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V39" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12293,7 +11946,7 @@
         <v>14</v>
       </c>
       <c r="U40" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V40" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12480,7 +12133,7 @@
         <v>14</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V41" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12667,7 +12320,7 @@
         <v>16</v>
       </c>
       <c r="U42" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V42" s="12" t="n">
         <v>100.2213974036418</v>
@@ -12854,7 +12507,7 @@
         <v>16</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V43" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13041,7 +12694,7 @@
         <v>27</v>
       </c>
       <c r="U44" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V44" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13228,7 +12881,7 @@
         <v>27</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V45" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13415,7 +13068,7 @@
         <v>26</v>
       </c>
       <c r="U46" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V46" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13602,7 +13255,7 @@
         <v>32</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V47" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13789,7 +13442,7 @@
         <v>66</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V48" s="12" t="n">
         <v>100.2213974036418</v>
@@ -13976,7 +13629,7 @@
         <v>57</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V49" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14163,7 +13816,7 @@
         <v>15</v>
       </c>
       <c r="U50" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V50" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14350,7 +14003,7 @@
         <v>91</v>
       </c>
       <c r="U51" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V51" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14537,7 +14190,7 @@
         <v>42</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V52" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14724,7 +14377,7 @@
         <v>125</v>
       </c>
       <c r="U53" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V53" s="12" t="n">
         <v>100.2213974036418</v>
@@ -14911,7 +14564,7 @@
         <v>26</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V54" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15098,7 +14751,7 @@
         <v>38</v>
       </c>
       <c r="U55" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V55" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15285,7 +14938,7 @@
         <v>35</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V56" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15472,7 +15125,7 @@
         <v>28</v>
       </c>
       <c r="U57" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V57" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15659,7 +15312,7 @@
         <v>28</v>
       </c>
       <c r="U58" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V58" s="12" t="n">
         <v>100.2213974036418</v>
@@ -15846,7 +15499,7 @@
         <v>27</v>
       </c>
       <c r="U59" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V59" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16033,7 +15686,7 @@
         <v>24</v>
       </c>
       <c r="U60" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V60" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16220,7 +15873,7 @@
         <v>47</v>
       </c>
       <c r="U61" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V61" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16407,7 +16060,7 @@
         <v>47</v>
       </c>
       <c r="U62" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V62" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16594,7 +16247,7 @@
         <v>27</v>
       </c>
       <c r="U63" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V63" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16781,7 +16434,7 @@
         <v>26</v>
       </c>
       <c r="U64" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V64" s="12" t="n">
         <v>100.2213974036418</v>
@@ -16968,7 +16621,7 @@
         <v>32</v>
       </c>
       <c r="U65" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V65" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17155,7 +16808,7 @@
         <v>15</v>
       </c>
       <c r="U66" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V66" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17342,7 +16995,7 @@
         <v>31</v>
       </c>
       <c r="U67" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V67" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17529,7 +17182,7 @@
         <v>26</v>
       </c>
       <c r="U68" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V68" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17716,7 +17369,7 @@
         <v>20</v>
       </c>
       <c r="U69" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V69" s="12" t="n">
         <v>100.2213974036418</v>
@@ -17903,7 +17556,7 @@
         <v>26</v>
       </c>
       <c r="U70" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V70" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18090,7 +17743,7 @@
         <v>71</v>
       </c>
       <c r="U71" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V71" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18277,7 +17930,7 @@
         <v>108</v>
       </c>
       <c r="U72" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V72" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18464,7 +18117,7 @@
         <v>20</v>
       </c>
       <c r="U73" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V73" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18651,7 +18304,7 @@
         <v>38</v>
       </c>
       <c r="U74" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V74" s="12" t="n">
         <v>100.2213974036418</v>
@@ -18838,7 +18491,7 @@
         <v>43</v>
       </c>
       <c r="U75" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V75" s="12" t="n">
         <v>100.2213974036418</v>
@@ -19025,7 +18678,7 @@
         <v>25</v>
       </c>
       <c r="U76" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V76" s="12" t="n">
         <v>100.2213974036418</v>
@@ -19212,7 +18865,7 @@
         <v>13</v>
       </c>
       <c r="U77" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V77" s="12" t="n">
         <v>100.2213974036418</v>
@@ -19399,7 +19052,7 @@
         <v>25</v>
       </c>
       <c r="U78" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V78" s="12" t="n">
         <v>100.2213974036418</v>
@@ -19586,7 +19239,7 @@
         <v>17</v>
       </c>
       <c r="U79" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V79" s="12" t="n">
         <v>100.2213974036418</v>
@@ -19773,7 +19426,7 @@
         <v>23</v>
       </c>
       <c r="U80" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V80" s="12" t="n">
         <v>100.2213974036418</v>
@@ -19960,7 +19613,7 @@
         <v>49</v>
       </c>
       <c r="U81" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V81" s="12" t="n">
         <v>100.2213974036418</v>
@@ -20147,7 +19800,7 @@
         <v>14</v>
       </c>
       <c r="U82" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V82" s="12" t="n">
         <v>100.2213974036418</v>
@@ -20334,7 +19987,7 @@
         <v>19</v>
       </c>
       <c r="U83" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V83" s="12" t="n">
         <v>100.2213974036418</v>
@@ -20521,7 +20174,7 @@
         <v>37</v>
       </c>
       <c r="U84" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V84" s="12" t="n">
         <v>100.2213974036418</v>
@@ -20708,7 +20361,7 @@
         <v>44</v>
       </c>
       <c r="U85" s="13" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="V85" s="12" t="n">
         <v>100.2213974036418</v>
